--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="276">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,6 +123,18 @@
     <t>Potassium [Moles/volume] in Serum or Plasma</t>
   </si>
   <si>
+    <t>2075-0</t>
+  </si>
+  <si>
+    <t>Chloride [Moles/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3094-0</t>
+  </si>
+  <si>
+    <t>Urea nitrogen [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
     <t>5810-7</t>
   </si>
   <si>
@@ -138,49 +150,85 @@
     <t>89024-4</t>
   </si>
   <si>
-    <t>Hearing threshold Ear-left 500 Hz [dB]</t>
+    <t>Hearing threshold Ear - left --500 Hz</t>
   </si>
   <si>
     <t>89016-0</t>
   </si>
   <si>
-    <t>Hearing threshold Ear-left 1000 Hz [dB]</t>
+    <t>Hearing threshold Ear - left --1000 Hz</t>
+  </si>
+  <si>
+    <t>89018-6</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - left --2000 Hz</t>
+  </si>
+  <si>
+    <t>89020-2</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - left --3000 Hz</t>
+  </si>
+  <si>
+    <t>89022-8</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - left --4000 Hz</t>
+  </si>
+  <si>
+    <t>89026-9</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - left --6000 Hz</t>
+  </si>
+  <si>
+    <t>89028-5</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - left --8000 Hz</t>
+  </si>
+  <si>
+    <t>89025-1</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - right --500 Hz</t>
   </si>
   <si>
     <t>89017-8</t>
   </si>
   <si>
-    <t>Hearing threshold Ear-left 2000 Hz [dB]</t>
-  </si>
-  <si>
-    <t>89018-6</t>
-  </si>
-  <si>
-    <t>Hearing threshold Ear-left 4000 Hz [dB]</t>
-  </si>
-  <si>
-    <t>89028-5</t>
-  </si>
-  <si>
-    <t>Hearing threshold Ear-right 500 Hz [dB]</t>
-  </si>
-  <si>
-    <t>89020-2</t>
-  </si>
-  <si>
-    <t>Hearing threshold Ear-right 1000 Hz [dB]</t>
+    <t>Hearing threshold Ear - right --1000 Hz</t>
   </si>
   <si>
     <t>89019-4</t>
   </si>
   <si>
-    <t>Hearing threshold Ear-right 2000 Hz [dB]</t>
-  </si>
-  <si>
-    <t>89022-8</t>
-  </si>
-  <si>
-    <t>Hearing threshold Ear-right 4000 Hz [dB]</t>
+    <t>Hearing threshold Ear - right --2000 Hz</t>
+  </si>
+  <si>
+    <t>89021-0</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - right --3000 Hz</t>
+  </si>
+  <si>
+    <t>89023-6</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - right --4000 Hz</t>
+  </si>
+  <si>
+    <t>89027-7</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - right --6000 Hz</t>
+  </si>
+  <si>
+    <t>89029-3</t>
+  </si>
+  <si>
+    <t>Hearing threshold Ear - right --8000 Hz</t>
   </si>
   <si>
     <t>789-8</t>
@@ -225,28 +273,40 @@
     <t>Lymphocytes [Fraction] of WBC</t>
   </si>
   <si>
+    <t>11580-8</t>
+  </si>
+  <si>
+    <t>Thyrotropin [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3024-7</t>
+  </si>
+  <si>
+    <t>Thyroxine (T4) free [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
     <t>24579-5</t>
   </si>
   <si>
     <t>XR Bones.long Survey</t>
   </si>
   <si>
-    <t>19868-9</t>
-  </si>
-  <si>
-    <t>FEV1 Vol Respiratory Spirometry</t>
-  </si>
-  <si>
     <t>19876-2</t>
   </si>
   <si>
-    <t>FVC Vol Respiratory Spirometry</t>
+    <t>Forced vital capacity [Volume] in Airways by Spirometry</t>
+  </si>
+  <si>
+    <t>20150-9</t>
+  </si>
+  <si>
+    <t>Forced expiratory volume in 1 second [Volume] in Airways by Spirometry</t>
   </si>
   <si>
     <t>19926-5</t>
   </si>
   <si>
-    <t>FEV1% or FEV1/FVC (%)</t>
+    <t>Forced expiratory volume in 1 second/Forced vital capacity [Volume Ratio] in Airways by Spirometry</t>
   </si>
   <si>
     <t>5671-3</t>
@@ -282,7 +342,19 @@
     <t>36643-5</t>
   </si>
   <si>
-    <t>XR Chest 2V</t>
+    <t>XR Chest 2 Views</t>
+  </si>
+  <si>
+    <t>24648-8</t>
+  </si>
+  <si>
+    <t>XR Chest PA upright</t>
+  </si>
+  <si>
+    <t>2324-2</t>
+  </si>
+  <si>
+    <t>Gamma glutamyltransferase [Enzymatic activity/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>6709-0</t>
@@ -541,6 +613,150 @@
   </si>
   <si>
     <t>MDMA [Presence] in Urine by Screening test</t>
+  </si>
+  <si>
+    <t>19177-5</t>
+  </si>
+  <si>
+    <t>Alpha-1-fetoprotein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2039-6</t>
+  </si>
+  <si>
+    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2857-1</t>
+  </si>
+  <si>
+    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>19199-9</t>
+  </si>
+  <si>
+    <t>10886-0</t>
+  </si>
+  <si>
+    <t>Prostate specific Ag.free [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>97149-9</t>
+  </si>
+  <si>
+    <t>[-2]pro-prostate specific antigen [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>97150-7</t>
+  </si>
+  <si>
+    <t>Prostate Health Index in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>10334-1</t>
+  </si>
+  <si>
+    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>83082-8</t>
+  </si>
+  <si>
+    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>83085-1</t>
+  </si>
+  <si>
+    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>24108-3</t>
+  </si>
+  <si>
+    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>83084-4</t>
+  </si>
+  <si>
+    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>83083-6</t>
+  </si>
+  <si>
+    <t>Cancer Ag 15-3 [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>83112-3</t>
+  </si>
+  <si>
+    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>1834-1</t>
+  </si>
+  <si>
+    <t>9679-2</t>
+  </si>
+  <si>
+    <t>Squamous cell carcinoma Ag [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>19113-0</t>
+  </si>
+  <si>
+    <t>IgE [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>9633-9</t>
+  </si>
+  <si>
+    <t>Epstein Barr virus VCA IgA Ab [Presence] in Serum</t>
+  </si>
+  <si>
+    <t>10835-7</t>
+  </si>
+  <si>
+    <t>Lipoprotein A [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1869-7</t>
+  </si>
+  <si>
+    <t>Apolipoprotein A-I [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1884-6</t>
+  </si>
+  <si>
+    <t>Apolipoprotein B [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>33762-6</t>
+  </si>
+  <si>
+    <t>Natriuretic peptide.proB-type N-terminal [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>42254-3</t>
+  </si>
+  <si>
+    <t>Nuclear Ab [Presence] in Serum by Immunofluorescence</t>
+  </si>
+  <si>
+    <t>11572-5</t>
+  </si>
+  <si>
+    <t>Rheumatoid factor [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>25390-6</t>
+  </si>
+  <si>
+    <t>CYFRA 21-1 [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>24606-6</t>
@@ -896,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B126"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1601,18 +1817,314 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>22</v>
+        <v>202</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>22</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="306">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -229,6 +229,96 @@
   </si>
   <si>
     <t>Hearing threshold Ear - right --8000 Hz</t>
+  </si>
+  <si>
+    <t>21104-5</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Audiometry study（panel 變異）</t>
+  </si>
+  <si>
+    <t>21106-0</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Left ear 500 Hz</t>
+  </si>
+  <si>
+    <t>21111-0</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Left ear 1000 Hz</t>
+  </si>
+  <si>
+    <t>21113-6</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Left ear 2000 Hz</t>
+  </si>
+  <si>
+    <t>21115-1</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Left ear 3000 Hz</t>
+  </si>
+  <si>
+    <t>21116-9</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Left ear 4000 Hz</t>
+  </si>
+  <si>
+    <t>21117-7</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Left ear 6000 Hz</t>
+  </si>
+  <si>
+    <t>21118-5</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Left ear 8000 Hz</t>
+  </si>
+  <si>
+    <t>21120-1</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Right ear 500 Hz</t>
+  </si>
+  <si>
+    <t>21123-5</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Right ear 1000 Hz</t>
+  </si>
+  <si>
+    <t>21125-0</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Right ear 2000 Hz</t>
+  </si>
+  <si>
+    <t>21127-6</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Right ear 3000 Hz</t>
+  </si>
+  <si>
+    <t>21128-4</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Right ear 4000 Hz</t>
+  </si>
+  <si>
+    <t>21129-2</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Right ear 6000 Hz</t>
+  </si>
+  <si>
+    <t>21130-0</t>
+  </si>
+  <si>
+    <t>Pure tone audiometry - Right ear 8000 Hz</t>
   </si>
   <si>
     <t>789-8</t>
@@ -1112,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B126"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1836,124 +1926,124 @@
         <v>206</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>201</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>235</v>
@@ -1961,90 +2051,90 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>257</v>
+        <v>231</v>
       </c>
     </row>
     <row r="117">
@@ -2113,18 +2203,138 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>22</v>
+        <v>274</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>22</v>
+        <v>275</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -925,6 +925,897 @@
   </si>
   <si>
     <t>DXA Skeletal Sys Views for BMD</t>
+  </si>
+  <si>
+    <t>10701-1</t>
+  </si>
+  <si>
+    <t>Ova and parasites [Presence] in Stool by Concentration method</t>
+  </si>
+  <si>
+    <t>10704-5</t>
+  </si>
+  <si>
+    <t>Ova and parasites [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>10834-0</t>
+  </si>
+  <si>
+    <t>Globulin [Mass/volume] in Serum or Plasma by calculation</t>
+  </si>
+  <si>
+    <t>11218-5</t>
+  </si>
+  <si>
+    <t>Microalbumin [Mass/volume] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>11277-1</t>
+  </si>
+  <si>
+    <t>Epithelial cells.squamous [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>12453-7</t>
+  </si>
+  <si>
+    <t>Amorphous phosphate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>12454-5</t>
+  </si>
+  <si>
+    <t>Amorphous urate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>13046-8</t>
+  </si>
+  <si>
+    <t>Atypical lymphocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>13047-6</t>
+  </si>
+  <si>
+    <t>Plasma cells/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>13655-6</t>
+  </si>
+  <si>
+    <t>Leukocytes [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>13658-0</t>
+  </si>
+  <si>
+    <t>Urobilinogen [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>13705-9</t>
+  </si>
+  <si>
+    <t>Albumin/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
+    <t>13945-1</t>
+  </si>
+  <si>
+    <t>Erythrocytes [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>13950-1</t>
+  </si>
+  <si>
+    <t>Hepatitis A virus IgM Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>13952-7</t>
+  </si>
+  <si>
+    <t>Hepatitis B virus core Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>14390-9</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
+  </si>
+  <si>
+    <t>14409-7</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
+  </si>
+  <si>
+    <t>14957-5</t>
+  </si>
+  <si>
+    <t>Microalbumin [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>1742-6</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1744-2</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+  </si>
+  <si>
+    <t>1751-7</t>
+  </si>
+  <si>
+    <t>Albumin [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1759-0</t>
+  </si>
+  <si>
+    <t>Albumin/Globulin [Mass Ratio] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>17780-8</t>
+  </si>
+  <si>
+    <t>Helicobacter pylori Ag [Presence] in Stool</t>
+  </si>
+  <si>
+    <t>1783-0</t>
+  </si>
+  <si>
+    <t>Alkaline phosphatase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>17861-6</t>
+  </si>
+  <si>
+    <t>Calcium [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1798-8</t>
+  </si>
+  <si>
+    <t>Amylase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>19048-8</t>
+  </si>
+  <si>
+    <t>Erythroblasts/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>1920-8</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1968-7</t>
+  </si>
+  <si>
+    <t>Bilirubin.direct [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1975-2</t>
+  </si>
+  <si>
+    <t>Bilirubin.total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>19868-9</t>
+  </si>
+  <si>
+    <t>Forced vital capacity [Volume] Respiratory system by Spirometry</t>
+  </si>
+  <si>
+    <t>1988-5</t>
+  </si>
+  <si>
+    <t>C reactive protein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>20448-7</t>
+  </si>
+  <si>
+    <t>Insulin [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>20456-0</t>
+  </si>
+  <si>
+    <t>Fungi yeast-like [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>20507-0</t>
+  </si>
+  <si>
+    <t>Reagin Ab [Presence] in Serum by RPR</t>
+  </si>
+  <si>
+    <t>20621-9</t>
+  </si>
+  <si>
+    <t>Albumin/Creatinine [Ratio] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>20627-6</t>
+  </si>
+  <si>
+    <t>Color of Urine</t>
+  </si>
+  <si>
+    <t>2132-9</t>
+  </si>
+  <si>
+    <t>Cobalamin (Vitamin B12) [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>21440-3</t>
+  </si>
+  <si>
+    <t>Human papilloma virus 16+18+31+33+35+45+51+52+56 DNA [Presence] in Cervix by Probe</t>
+  </si>
+  <si>
+    <t>2161-8</t>
+  </si>
+  <si>
+    <t>Creatinine [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>22322-2</t>
+  </si>
+  <si>
+    <t>Hepatitis B virus surface Ab [Units/volume] in Serum</t>
+  </si>
+  <si>
+    <t>2284-8</t>
+  </si>
+  <si>
+    <t>Folate [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2335-8</t>
+  </si>
+  <si>
+    <t>Hemoglobin [Presence] in Stool</t>
+  </si>
+  <si>
+    <t>24110-9</t>
+  </si>
+  <si>
+    <t>Treponema pallidum Ab [Presence] in Serum by Immunoassay</t>
+  </si>
+  <si>
+    <t>2428-1</t>
+  </si>
+  <si>
+    <t>Homocysteine [Moles/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>25145-4</t>
+  </si>
+  <si>
+    <t>Bacteria [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>2532-0</t>
+  </si>
+  <si>
+    <t>Lactate dehydrogenase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>26446-5</t>
+  </si>
+  <si>
+    <t>Blasts/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26450-7</t>
+  </si>
+  <si>
+    <t>Eosinophils/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26464-8</t>
+  </si>
+  <si>
+    <t>26478-8</t>
+  </si>
+  <si>
+    <t>Lymphocytes/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26485-3</t>
+  </si>
+  <si>
+    <t>Monocytes/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26498-6</t>
+  </si>
+  <si>
+    <t>Myelocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26505-8</t>
+  </si>
+  <si>
+    <t>Hypersegmented neutrophils/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26508-2</t>
+  </si>
+  <si>
+    <t>Neutrophils/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26511-6</t>
+  </si>
+  <si>
+    <t>Neutrophils.segmented/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26515-7</t>
+  </si>
+  <si>
+    <t>Platelets [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>26524-9</t>
+  </si>
+  <si>
+    <t>Promyelocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>28539-5</t>
+  </si>
+  <si>
+    <t>MCH [Entitic mass] by Automated count</t>
+  </si>
+  <si>
+    <t>28541-1</t>
+  </si>
+  <si>
+    <t>Metamyelocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>2885-2</t>
+  </si>
+  <si>
+    <t>Protein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>29771-3</t>
+  </si>
+  <si>
+    <t>Hemoglobin.occult [Mass/volume] in Stool by Immunochemical method</t>
+  </si>
+  <si>
+    <t>30004-6</t>
+  </si>
+  <si>
+    <t>Creatinine [Mass/volume] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>3016-3</t>
+  </si>
+  <si>
+    <t>Thyrotropin [Units/volume] in Serum or Plasma by 3rd IS</t>
+  </si>
+  <si>
+    <t>30180-4</t>
+  </si>
+  <si>
+    <t>Basophils/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>3026-2</t>
+  </si>
+  <si>
+    <t>Thyroxine (T4) total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3040-3</t>
+  </si>
+  <si>
+    <t>Lipase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>30413-9</t>
+  </si>
+  <si>
+    <t>Abnormal lymphocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30428-7</t>
+  </si>
+  <si>
+    <t>MCV [Entitic volume] by calculation</t>
+  </si>
+  <si>
+    <t>30441-0</t>
+  </si>
+  <si>
+    <t>Abnormal monocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30466-7</t>
+  </si>
+  <si>
+    <t>Promonocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>3051-0</t>
+  </si>
+  <si>
+    <t>Triiodothyronine (T3) free [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>30522-7</t>
+  </si>
+  <si>
+    <t>C reactive protein [Mass/volume] in Serum or Plasma by High sensitivity method</t>
+  </si>
+  <si>
+    <t>3053-6</t>
+  </si>
+  <si>
+    <t>Triiodothyronine (T3) total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3084-1</t>
+  </si>
+  <si>
+    <t>Uric acid [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>31147-2</t>
+  </si>
+  <si>
+    <t>Reagin Ab [Presence] in Serum by RPR -- titer</t>
+  </si>
+  <si>
+    <t>32356-8</t>
+  </si>
+  <si>
+    <t>Yeast [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>33218-9</t>
+  </si>
+  <si>
+    <t>Bacteria [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33219-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells.squamous [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33223-9</t>
+  </si>
+  <si>
+    <t>Hyaline casts [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33342-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33668-5</t>
+  </si>
+  <si>
+    <t>Erythrocytes [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>33863-2</t>
+  </si>
+  <si>
+    <t>Cystatin C [Mass/volume] in Serum, Plasma or Blood</t>
+  </si>
+  <si>
+    <t>33914-3</t>
+  </si>
+  <si>
+    <t>Glomerular filtration rate/1.73 sq M.predicted by MDRD equation</t>
+  </si>
+  <si>
+    <t>34921-7</t>
+  </si>
+  <si>
+    <t>Plasmacytoid lymphocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>42524-9</t>
+  </si>
+  <si>
+    <t>Mucus [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>43755-8</t>
+  </si>
+  <si>
+    <t>Casts [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>4548-4</t>
+  </si>
+  <si>
+    <t>Hemoglobin A1c/Hemoglobin.total in Blood</t>
+  </si>
+  <si>
+    <t>4588-0</t>
+  </si>
+  <si>
+    <t>Hemoglobin H/Hemoglobin.total in Blood</t>
+  </si>
+  <si>
+    <t>46419-8</t>
+  </si>
+  <si>
+    <t>Erythrocytes [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>46702-7</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>46986-6</t>
+  </si>
+  <si>
+    <t>Cholesterol in VLDL [Mass/volume] in Serum or Plasma by calculation</t>
+  </si>
+  <si>
+    <t>47214-2</t>
+  </si>
+  <si>
+    <t>Homeostasis model assessment</t>
+  </si>
+  <si>
+    <t>49154-8</t>
+  </si>
+  <si>
+    <t>Uric acid [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>50235-1</t>
+  </si>
+  <si>
+    <t>Mucus [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>50551-1</t>
+  </si>
+  <si>
+    <t>Bilirubin [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50555-2</t>
+  </si>
+  <si>
+    <t>Glucose [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50558-6</t>
+  </si>
+  <si>
+    <t>Nitrite [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50560-2</t>
+  </si>
+  <si>
+    <t>pH of Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50562-8</t>
+  </si>
+  <si>
+    <t>Specific gravity of Urine by Refractometer</t>
+  </si>
+  <si>
+    <t>5176-3</t>
+  </si>
+  <si>
+    <t>Helicobacter pylori IgG Ab [Presence] in Serum</t>
+  </si>
+  <si>
+    <t>51913-2</t>
+  </si>
+  <si>
+    <t>Hepatitis A virus Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5193-8</t>
+  </si>
+  <si>
+    <t>Hepatitis B virus surface Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>53324-0</t>
+  </si>
+  <si>
+    <t>Spermatozoa [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>5334-8</t>
+  </si>
+  <si>
+    <t>Rubella virus IgG Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>53975-9</t>
+  </si>
+  <si>
+    <t>Drug crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5403-1</t>
+  </si>
+  <si>
+    <t>Varicella zoster virus IgG Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>56888-1</t>
+  </si>
+  <si>
+    <t>HIV 1 and 2 Ag and Ab panel [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5766-1</t>
+  </si>
+  <si>
+    <t>Ammonium acid urate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5770-3</t>
+  </si>
+  <si>
+    <t>5771-1</t>
+  </si>
+  <si>
+    <t>Bilirubin crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5773-7</t>
+  </si>
+  <si>
+    <t>Calcium carbonate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>57734-6</t>
+  </si>
+  <si>
+    <t>Ketones [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5774-5</t>
+  </si>
+  <si>
+    <t>Calcium oxalate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5775-2</t>
+  </si>
+  <si>
+    <t>Calcium phosphate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>57751-0</t>
+  </si>
+  <si>
+    <t>Hemoglobin [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5777-8</t>
+  </si>
+  <si>
+    <t>Cholesterol crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5784-4</t>
+  </si>
+  <si>
+    <t>Cystine crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5787-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>5788-5</t>
+  </si>
+  <si>
+    <t>Oval fat bodies [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>5792-7</t>
+  </si>
+  <si>
+    <t>5794-3</t>
+  </si>
+  <si>
+    <t>5796-8</t>
+  </si>
+  <si>
+    <t>Hyaline casts [#/area] in Urine sediment by Microscopy low power field</t>
+  </si>
+  <si>
+    <t>5797-6</t>
+  </si>
+  <si>
+    <t>5799-2</t>
+  </si>
+  <si>
+    <t>Leukocyte esterase [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5802-4</t>
+  </si>
+  <si>
+    <t>5803-2</t>
+  </si>
+  <si>
+    <t>5813-1</t>
+  </si>
+  <si>
+    <t>Trichomonas vaginalis [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5814-9</t>
+  </si>
+  <si>
+    <t>Calcium magnesium ammonium phosphate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5817-2</t>
+  </si>
+  <si>
+    <t>Uric acid crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5821-4</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>5905-5</t>
+  </si>
+  <si>
+    <t>Monocytes/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>59261-8</t>
+  </si>
+  <si>
+    <t>Hemoglobin A1c/Hemoglobin.total in Blood by IFCC protocol</t>
+  </si>
+  <si>
+    <t>60026-2</t>
+  </si>
+  <si>
+    <t>62292-8</t>
+  </si>
+  <si>
+    <t>25-hydroxyvitamin D3 [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>62487-4</t>
+  </si>
+  <si>
+    <t>6768-6</t>
+  </si>
+  <si>
+    <t>70028-6</t>
+  </si>
+  <si>
+    <t>Megakaryocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>706-2</t>
+  </si>
+  <si>
+    <t>Basophils/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>713-8</t>
+  </si>
+  <si>
+    <t>Eosinophils/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>731-0</t>
+  </si>
+  <si>
+    <t>Lymphocytes [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>751-8</t>
+  </si>
+  <si>
+    <t>Neutrophils [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>785-6</t>
+  </si>
+  <si>
+    <t>786-4</t>
+  </si>
+  <si>
+    <t>MCHC [Mass/volume] by Automated count</t>
+  </si>
+  <si>
+    <t>787-2</t>
+  </si>
+  <si>
+    <t>MCV [Entitic volume] by Automated count</t>
+  </si>
+  <si>
+    <t>788-0</t>
+  </si>
+  <si>
+    <t>Erythrocyte distribution width [Ratio] by Automated count</t>
+  </si>
+  <si>
+    <t>7962-4</t>
+  </si>
+  <si>
+    <t>Measles virus IgG Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>79880-1</t>
+  </si>
+  <si>
+    <t>Vision test panel</t>
+  </si>
+  <si>
+    <t>804-5</t>
+  </si>
+  <si>
+    <t>WBC [#/volume] in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>8099-4</t>
+  </si>
+  <si>
+    <t>Thyroid peroxidase Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>88112-8</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+  </si>
+  <si>
+    <t>88293-6</t>
+  </si>
+  <si>
+    <t>Glomerular filtration rate/1.73 sq M.predicted by Creatinine-based formula (CKD-EPI 2021)</t>
+  </si>
+  <si>
+    <t>9397-1</t>
+  </si>
+  <si>
+    <t>Color of Stool</t>
+  </si>
+  <si>
+    <t>9830-1</t>
+  </si>
+  <si>
+    <t>Cholesterol/Cholesterol in HDL [Mass Ratio] in Serum or Plasma</t>
   </si>
   <si>
     <t>System URI</t>
@@ -1202,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2323,18 +3214,1250 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>22</v>
+        <v>304</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>22</v>
+        <v>305</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B278" t="s" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B279" t="s" s="2">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B280" t="s" s="2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B286" t="s" s="2">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B287" t="s" s="2">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B288" t="s" s="2">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B290" t="s" s="2">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B292" t="s" s="2">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>602</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -144,7 +144,7 @@
     <t>89015-2</t>
   </si>
   <si>
-    <t>Pure tone threshold audiometry panel</t>
+    <t>Pure tone air conduction threshold audiometry panel</t>
   </si>
   <si>
     <t>89024-4</t>
@@ -384,19 +384,19 @@
     <t>19876-2</t>
   </si>
   <si>
-    <t>Forced vital capacity [Volume] in Airways by Spirometry</t>
+    <t>Forced vital capacity [Volume] Respiratory system by Spirometry --pre bronchodilation</t>
   </si>
   <si>
     <t>20150-9</t>
   </si>
   <si>
-    <t>Forced expiratory volume in 1 second [Volume] in Airways by Spirometry</t>
+    <t>FEV1</t>
   </si>
   <si>
     <t>19926-5</t>
   </si>
   <si>
-    <t>Forced expiratory volume in 1 second/Forced vital capacity [Volume Ratio] in Airways by Spirometry</t>
+    <t>FEV1/FVC</t>
   </si>
   <si>
     <t>5671-3</t>
@@ -852,7 +852,7 @@
     <t>24606-6</t>
   </si>
   <si>
-    <t>Mammogram screening views study</t>
+    <t>MG Breast Screening</t>
   </si>
   <si>
     <t>103892-6</t>
@@ -927,6 +927,843 @@
     <t>DXA Skeletal Sys Views for BMD</t>
   </si>
   <si>
+    <t>13046-8</t>
+  </si>
+  <si>
+    <t>Atypical lymphocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>13047-6</t>
+  </si>
+  <si>
+    <t>Plasma cells/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>19048-8</t>
+  </si>
+  <si>
+    <t>Erythroblasts/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>26446-5</t>
+  </si>
+  <si>
+    <t>Blasts/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26450-7</t>
+  </si>
+  <si>
+    <t>Eosinophils/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26464-8</t>
+  </si>
+  <si>
+    <t>26478-8</t>
+  </si>
+  <si>
+    <t>Lymphocytes/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26485-3</t>
+  </si>
+  <si>
+    <t>Monocytes/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26498-6</t>
+  </si>
+  <si>
+    <t>Myelocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26505-8</t>
+  </si>
+  <si>
+    <t>Hypersegmented neutrophils/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26508-2</t>
+  </si>
+  <si>
+    <t>Neutrophils/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26511-6</t>
+  </si>
+  <si>
+    <t>Neutrophils.segmented/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26515-7</t>
+  </si>
+  <si>
+    <t>Platelets [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>26524-9</t>
+  </si>
+  <si>
+    <t>Promyelocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>28539-5</t>
+  </si>
+  <si>
+    <t>MCH [Entitic mass] by Automated count</t>
+  </si>
+  <si>
+    <t>28541-1</t>
+  </si>
+  <si>
+    <t>Metamyelocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30180-4</t>
+  </si>
+  <si>
+    <t>Basophils/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>30413-9</t>
+  </si>
+  <si>
+    <t>Abnormal lymphocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30428-7</t>
+  </si>
+  <si>
+    <t>MCV [Entitic volume] by calculation</t>
+  </si>
+  <si>
+    <t>30441-0</t>
+  </si>
+  <si>
+    <t>Abnormal monocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30466-7</t>
+  </si>
+  <si>
+    <t>Promonocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>34921-7</t>
+  </si>
+  <si>
+    <t>Plasmacytoid lymphocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>5905-5</t>
+  </si>
+  <si>
+    <t>Monocytes/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>70028-6</t>
+  </si>
+  <si>
+    <t>Megakaryocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>706-2</t>
+  </si>
+  <si>
+    <t>Basophils/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>713-8</t>
+  </si>
+  <si>
+    <t>Eosinophils/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>731-0</t>
+  </si>
+  <si>
+    <t>Lymphocytes [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>751-8</t>
+  </si>
+  <si>
+    <t>Neutrophils [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>785-6</t>
+  </si>
+  <si>
+    <t>786-4</t>
+  </si>
+  <si>
+    <t>MCHC [Mass/volume] by Automated count</t>
+  </si>
+  <si>
+    <t>787-2</t>
+  </si>
+  <si>
+    <t>MCV [Entitic volume] by Automated count</t>
+  </si>
+  <si>
+    <t>788-0</t>
+  </si>
+  <si>
+    <t>Erythrocyte distribution width [Ratio] by Automated count</t>
+  </si>
+  <si>
+    <t>804-5</t>
+  </si>
+  <si>
+    <t>WBC [#/volume] in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>17861-6</t>
+  </si>
+  <si>
+    <t>Calcium [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>20448-7</t>
+  </si>
+  <si>
+    <t>Insulin [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2428-1</t>
+  </si>
+  <si>
+    <t>Homocysteine [Moles/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>30522-7</t>
+  </si>
+  <si>
+    <t>C reactive protein [Mass/volume] in Serum or Plasma by High sensitivity method</t>
+  </si>
+  <si>
+    <t>3084-1</t>
+  </si>
+  <si>
+    <t>Uric acid [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>33863-2</t>
+  </si>
+  <si>
+    <t>Cystatin C [Mass/volume] in Serum, Plasma or Blood</t>
+  </si>
+  <si>
+    <t>33914-3</t>
+  </si>
+  <si>
+    <t>Glomerular filtration rate/1.73 sq M.predicted by MDRD equation</t>
+  </si>
+  <si>
+    <t>4548-4</t>
+  </si>
+  <si>
+    <t>Hemoglobin A1c/Hemoglobin.total in Blood</t>
+  </si>
+  <si>
+    <t>47214-2</t>
+  </si>
+  <si>
+    <t>Homeostasis model assessment</t>
+  </si>
+  <si>
+    <t>49154-8</t>
+  </si>
+  <si>
+    <t>Uric acid [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>59261-8</t>
+  </si>
+  <si>
+    <t>Hemoglobin A1c/Hemoglobin.total in Blood by IFCC protocol</t>
+  </si>
+  <si>
+    <t>98979-8</t>
+  </si>
+  <si>
+    <t>Glomerular filtration rate [Volume Rate/Area] in Serum, Plasma or Blood by Creatinine-based formula (CKD-EPI 2021)/1.73 sq M</t>
+  </si>
+  <si>
+    <t>10834-0</t>
+  </si>
+  <si>
+    <t>Globulin [Mass/volume] in Serum or Plasma by calculation</t>
+  </si>
+  <si>
+    <t>14390-9</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
+  </si>
+  <si>
+    <t>14409-7</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
+  </si>
+  <si>
+    <t>1742-6</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1744-2</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+  </si>
+  <si>
+    <t>1751-7</t>
+  </si>
+  <si>
+    <t>Albumin [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1759-0</t>
+  </si>
+  <si>
+    <t>Albumin/Globulin [Mass Ratio] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1783-0</t>
+  </si>
+  <si>
+    <t>Alkaline phosphatase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1798-8</t>
+  </si>
+  <si>
+    <t>Amylase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1920-8</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1968-7</t>
+  </si>
+  <si>
+    <t>Bilirubin.direct [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1975-2</t>
+  </si>
+  <si>
+    <t>Bilirubin.total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2532-0</t>
+  </si>
+  <si>
+    <t>Lactate dehydrogenase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2885-2</t>
+  </si>
+  <si>
+    <t>Protein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3040-3</t>
+  </si>
+  <si>
+    <t>Lipase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>6768-6</t>
+  </si>
+  <si>
+    <t>88112-8</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+  </si>
+  <si>
+    <t>46986-6</t>
+  </si>
+  <si>
+    <t>Cholesterol in VLDL [Mass/volume] in Serum or Plasma by calculation</t>
+  </si>
+  <si>
+    <t>9830-1</t>
+  </si>
+  <si>
+    <t>Cholesterol/Cholesterol in HDL [Mass Ratio] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2132-9</t>
+  </si>
+  <si>
+    <t>Cobalamin (Vitamin B12) [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2284-8</t>
+  </si>
+  <si>
+    <t>Folate [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3016-3</t>
+  </si>
+  <si>
+    <t>Thyrotropin [Units/volume] in Serum or Plasma by 3rd IS</t>
+  </si>
+  <si>
+    <t>3026-2</t>
+  </si>
+  <si>
+    <t>Thyroxine (T4) total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3051-0</t>
+  </si>
+  <si>
+    <t>Triiodothyronine (T3) free [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3053-6</t>
+  </si>
+  <si>
+    <t>Triiodothyronine (T3) total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>62292-8</t>
+  </si>
+  <si>
+    <t>25-hydroxyvitamin D3 [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>8099-4</t>
+  </si>
+  <si>
+    <t>Thyroid peroxidase Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>13950-1</t>
+  </si>
+  <si>
+    <t>Hepatitis A virus IgM Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>13952-7</t>
+  </si>
+  <si>
+    <t>Hepatitis B virus core Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>17780-8</t>
+  </si>
+  <si>
+    <t>Helicobacter pylori Ag [Presence] in Stool</t>
+  </si>
+  <si>
+    <t>20507-0</t>
+  </si>
+  <si>
+    <t>Reagin Ab [Presence] in Serum by RPR</t>
+  </si>
+  <si>
+    <t>21440-3</t>
+  </si>
+  <si>
+    <t>Human papilloma virus 16+18+31+33+35+45+51+52+56 DNA [Presence] in Cervix by Probe</t>
+  </si>
+  <si>
+    <t>22322-2</t>
+  </si>
+  <si>
+    <t>Hepatitis B virus surface Ab [Units/volume] in Serum</t>
+  </si>
+  <si>
+    <t>24110-9</t>
+  </si>
+  <si>
+    <t>Treponema pallidum Ab [Presence] in Serum by Immunoassay</t>
+  </si>
+  <si>
+    <t>29771-3</t>
+  </si>
+  <si>
+    <t>Hemoglobin.occult [Mass/volume] in Stool by Immunochemical method</t>
+  </si>
+  <si>
+    <t>31147-2</t>
+  </si>
+  <si>
+    <t>Reagin Ab [Presence] in Serum by RPR -- titer</t>
+  </si>
+  <si>
+    <t>5176-3</t>
+  </si>
+  <si>
+    <t>Helicobacter pylori IgG Ab [Presence] in Serum</t>
+  </si>
+  <si>
+    <t>51913-2</t>
+  </si>
+  <si>
+    <t>Hepatitis A virus Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5193-8</t>
+  </si>
+  <si>
+    <t>Hepatitis B virus surface Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5334-8</t>
+  </si>
+  <si>
+    <t>Rubella virus IgG Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5403-1</t>
+  </si>
+  <si>
+    <t>Varicella zoster virus IgG Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>56888-1</t>
+  </si>
+  <si>
+    <t>HIV 1 and 2 Ag and Ab panel [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>7962-4</t>
+  </si>
+  <si>
+    <t>Measles virus IgG Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>11218-5</t>
+  </si>
+  <si>
+    <t>Microalbumin [Mass/volume] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>11277-1</t>
+  </si>
+  <si>
+    <t>Epithelial cells.squamous [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>12453-7</t>
+  </si>
+  <si>
+    <t>Amorphous phosphate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>12454-5</t>
+  </si>
+  <si>
+    <t>Amorphous urate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>13658-0</t>
+  </si>
+  <si>
+    <t>Urobilinogen [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>13945-1</t>
+  </si>
+  <si>
+    <t>Erythrocytes [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>20456-0</t>
+  </si>
+  <si>
+    <t>Fungi yeast-like [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>20621-9</t>
+  </si>
+  <si>
+    <t>Albumin/Creatinine [Ratio] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>20627-6</t>
+  </si>
+  <si>
+    <t>Color of Urine</t>
+  </si>
+  <si>
+    <t>25145-4</t>
+  </si>
+  <si>
+    <t>Bacteria [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>30004-6</t>
+  </si>
+  <si>
+    <t>Creatinine [Mass/volume] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>32356-8</t>
+  </si>
+  <si>
+    <t>Yeast [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>33218-9</t>
+  </si>
+  <si>
+    <t>Bacteria [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33219-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells.squamous [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33223-9</t>
+  </si>
+  <si>
+    <t>Hyaline casts [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33342-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>43755-8</t>
+  </si>
+  <si>
+    <t>Casts [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>46419-8</t>
+  </si>
+  <si>
+    <t>Erythrocytes [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>46702-7</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>50235-1</t>
+  </si>
+  <si>
+    <t>Mucus [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>50551-1</t>
+  </si>
+  <si>
+    <t>Bilirubin [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50555-2</t>
+  </si>
+  <si>
+    <t>Glucose [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50558-6</t>
+  </si>
+  <si>
+    <t>Nitrite [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50560-2</t>
+  </si>
+  <si>
+    <t>pH of Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50562-8</t>
+  </si>
+  <si>
+    <t>Specific gravity of Urine by Refractometer</t>
+  </si>
+  <si>
+    <t>53324-0</t>
+  </si>
+  <si>
+    <t>Spermatozoa [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>53975-9</t>
+  </si>
+  <si>
+    <t>Drug crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5766-1</t>
+  </si>
+  <si>
+    <t>Ammonium acid urate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5770-3</t>
+  </si>
+  <si>
+    <t>5771-1</t>
+  </si>
+  <si>
+    <t>Bilirubin crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5773-7</t>
+  </si>
+  <si>
+    <t>Calcium carbonate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>57734-6</t>
+  </si>
+  <si>
+    <t>Ketones [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5774-5</t>
+  </si>
+  <si>
+    <t>Calcium oxalate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5775-2</t>
+  </si>
+  <si>
+    <t>Calcium phosphate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>57751-0</t>
+  </si>
+  <si>
+    <t>Hemoglobin [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5777-8</t>
+  </si>
+  <si>
+    <t>Cholesterol crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5784-4</t>
+  </si>
+  <si>
+    <t>Cystine crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5787-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>5788-5</t>
+  </si>
+  <si>
+    <t>Oval fat bodies [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>5792-7</t>
+  </si>
+  <si>
+    <t>5794-3</t>
+  </si>
+  <si>
+    <t>5796-8</t>
+  </si>
+  <si>
+    <t>Hyaline casts [#/area] in Urine sediment by Microscopy low power field</t>
+  </si>
+  <si>
+    <t>5797-6</t>
+  </si>
+  <si>
+    <t>5799-2</t>
+  </si>
+  <si>
+    <t>Leukocyte esterase [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5802-4</t>
+  </si>
+  <si>
+    <t>5803-2</t>
+  </si>
+  <si>
+    <t>5813-1</t>
+  </si>
+  <si>
+    <t>Trichomonas vaginalis [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5814-9</t>
+  </si>
+  <si>
+    <t>Calcium magnesium ammonium phosphate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5817-2</t>
+  </si>
+  <si>
+    <t>Uric acid crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5821-4</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>60026-2</t>
+  </si>
+  <si>
+    <t>62487-4</t>
+  </si>
+  <si>
+    <t>13705-9</t>
+  </si>
+  <si>
+    <t>Albumin/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
+    <t>14957-5</t>
+  </si>
+  <si>
+    <t>Microalbumin [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>1988-5</t>
+  </si>
+  <si>
+    <t>C reactive protein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2161-8</t>
+  </si>
+  <si>
+    <t>Creatinine [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>4588-0</t>
+  </si>
+  <si>
+    <t>Hemoglobin H/Hemoglobin.total in Blood</t>
+  </si>
+  <si>
     <t>10701-1</t>
   </si>
   <si>
@@ -939,172 +1776,34 @@
     <t>Ova and parasites [Presence] in Stool by Microscopy</t>
   </si>
   <si>
-    <t>10834-0</t>
-  </si>
-  <si>
-    <t>Globulin [Mass/volume] in Serum or Plasma by calculation</t>
-  </si>
-  <si>
-    <t>11218-5</t>
-  </si>
-  <si>
-    <t>Microalbumin [Mass/volume] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>11277-1</t>
-  </si>
-  <si>
-    <t>Epithelial cells.squamous [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>12453-7</t>
-  </si>
-  <si>
-    <t>Amorphous phosphate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>12454-5</t>
-  </si>
-  <si>
-    <t>Amorphous urate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>13046-8</t>
-  </si>
-  <si>
-    <t>Atypical lymphocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>13047-6</t>
-  </si>
-  <si>
-    <t>Plasma cells/100 leukocytes in Blood</t>
-  </si>
-  <si>
     <t>13655-6</t>
   </si>
   <si>
     <t>Leukocytes [Presence] in Stool by Microscopy</t>
   </si>
   <si>
-    <t>13658-0</t>
-  </si>
-  <si>
-    <t>Urobilinogen [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>13705-9</t>
-  </si>
-  <si>
-    <t>Albumin/Creatinine [Mass Ratio] in Urine</t>
-  </si>
-  <si>
-    <t>13945-1</t>
-  </si>
-  <si>
-    <t>Erythrocytes [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>13950-1</t>
-  </si>
-  <si>
-    <t>Hepatitis A virus IgM Ab [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>13952-7</t>
-  </si>
-  <si>
-    <t>Hepatitis B virus core Ab [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>14390-9</t>
-  </si>
-  <si>
-    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
-  </si>
-  <si>
-    <t>14409-7</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
-  </si>
-  <si>
-    <t>14957-5</t>
-  </si>
-  <si>
-    <t>Microalbumin [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>1742-6</t>
-  </si>
-  <si>
-    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1744-2</t>
-  </si>
-  <si>
-    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
-  </si>
-  <si>
-    <t>1751-7</t>
-  </si>
-  <si>
-    <t>Albumin [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1759-0</t>
-  </si>
-  <si>
-    <t>Albumin/Globulin [Mass Ratio] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>17780-8</t>
-  </si>
-  <si>
-    <t>Helicobacter pylori Ag [Presence] in Stool</t>
-  </si>
-  <si>
-    <t>1783-0</t>
-  </si>
-  <si>
-    <t>Alkaline phosphatase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>17861-6</t>
-  </si>
-  <si>
-    <t>Calcium [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1798-8</t>
-  </si>
-  <si>
-    <t>Amylase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>19048-8</t>
-  </si>
-  <si>
-    <t>Erythroblasts/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>1920-8</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1968-7</t>
-  </si>
-  <si>
-    <t>Bilirubin.direct [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1975-2</t>
-  </si>
-  <si>
-    <t>Bilirubin.total [Mass/volume] in Serum or Plasma</t>
+    <t>2335-8</t>
+  </si>
+  <si>
+    <t>Hemoglobin [Presence] in Stool</t>
+  </si>
+  <si>
+    <t>33668-5</t>
+  </si>
+  <si>
+    <t>Erythrocytes [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>42524-9</t>
+  </si>
+  <si>
+    <t>Mucus [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>9397-1</t>
+  </si>
+  <si>
+    <t>Color of Stool</t>
   </si>
   <si>
     <t>19868-9</t>
@@ -1113,709 +1812,10 @@
     <t>Forced vital capacity [Volume] Respiratory system by Spirometry</t>
   </si>
   <si>
-    <t>1988-5</t>
-  </si>
-  <si>
-    <t>C reactive protein [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>20448-7</t>
-  </si>
-  <si>
-    <t>Insulin [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>20456-0</t>
-  </si>
-  <si>
-    <t>Fungi yeast-like [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>20507-0</t>
-  </si>
-  <si>
-    <t>Reagin Ab [Presence] in Serum by RPR</t>
-  </si>
-  <si>
-    <t>20621-9</t>
-  </si>
-  <si>
-    <t>Albumin/Creatinine [Ratio] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>20627-6</t>
-  </si>
-  <si>
-    <t>Color of Urine</t>
-  </si>
-  <si>
-    <t>2132-9</t>
-  </si>
-  <si>
-    <t>Cobalamin (Vitamin B12) [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>21440-3</t>
-  </si>
-  <si>
-    <t>Human papilloma virus 16+18+31+33+35+45+51+52+56 DNA [Presence] in Cervix by Probe</t>
-  </si>
-  <si>
-    <t>2161-8</t>
-  </si>
-  <si>
-    <t>Creatinine [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>22322-2</t>
-  </si>
-  <si>
-    <t>Hepatitis B virus surface Ab [Units/volume] in Serum</t>
-  </si>
-  <si>
-    <t>2284-8</t>
-  </si>
-  <si>
-    <t>Folate [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2335-8</t>
-  </si>
-  <si>
-    <t>Hemoglobin [Presence] in Stool</t>
-  </si>
-  <si>
-    <t>24110-9</t>
-  </si>
-  <si>
-    <t>Treponema pallidum Ab [Presence] in Serum by Immunoassay</t>
-  </si>
-  <si>
-    <t>2428-1</t>
-  </si>
-  <si>
-    <t>Homocysteine [Moles/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>25145-4</t>
-  </si>
-  <si>
-    <t>Bacteria [Presence] in Urine sediment by Light microscopy</t>
-  </si>
-  <si>
-    <t>2532-0</t>
-  </si>
-  <si>
-    <t>Lactate dehydrogenase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>26446-5</t>
-  </si>
-  <si>
-    <t>Blasts/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26450-7</t>
-  </si>
-  <si>
-    <t>Eosinophils/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26464-8</t>
-  </si>
-  <si>
-    <t>26478-8</t>
-  </si>
-  <si>
-    <t>Lymphocytes/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26485-3</t>
-  </si>
-  <si>
-    <t>Monocytes/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26498-6</t>
-  </si>
-  <si>
-    <t>Myelocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26505-8</t>
-  </si>
-  <si>
-    <t>Hypersegmented neutrophils/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26508-2</t>
-  </si>
-  <si>
-    <t>Neutrophils/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26511-6</t>
-  </si>
-  <si>
-    <t>Neutrophils.segmented/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26515-7</t>
-  </si>
-  <si>
-    <t>Platelets [#/volume] in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>26524-9</t>
-  </si>
-  <si>
-    <t>Promyelocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>28539-5</t>
-  </si>
-  <si>
-    <t>MCH [Entitic mass] by Automated count</t>
-  </si>
-  <si>
-    <t>28541-1</t>
-  </si>
-  <si>
-    <t>Metamyelocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>2885-2</t>
-  </si>
-  <si>
-    <t>Protein [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>29771-3</t>
-  </si>
-  <si>
-    <t>Hemoglobin.occult [Mass/volume] in Stool by Immunochemical method</t>
-  </si>
-  <si>
-    <t>30004-6</t>
-  </si>
-  <si>
-    <t>Creatinine [Mass/volume] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>3016-3</t>
-  </si>
-  <si>
-    <t>Thyrotropin [Units/volume] in Serum or Plasma by 3rd IS</t>
-  </si>
-  <si>
-    <t>30180-4</t>
-  </si>
-  <si>
-    <t>Basophils/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>3026-2</t>
-  </si>
-  <si>
-    <t>Thyroxine (T4) total [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>3040-3</t>
-  </si>
-  <si>
-    <t>Lipase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>30413-9</t>
-  </si>
-  <si>
-    <t>Abnormal lymphocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>30428-7</t>
-  </si>
-  <si>
-    <t>MCV [Entitic volume] by calculation</t>
-  </si>
-  <si>
-    <t>30441-0</t>
-  </si>
-  <si>
-    <t>Abnormal monocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>30466-7</t>
-  </si>
-  <si>
-    <t>Promonocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>3051-0</t>
-  </si>
-  <si>
-    <t>Triiodothyronine (T3) free [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>30522-7</t>
-  </si>
-  <si>
-    <t>C reactive protein [Mass/volume] in Serum or Plasma by High sensitivity method</t>
-  </si>
-  <si>
-    <t>3053-6</t>
-  </si>
-  <si>
-    <t>Triiodothyronine (T3) total [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>3084-1</t>
-  </si>
-  <si>
-    <t>Uric acid [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>31147-2</t>
-  </si>
-  <si>
-    <t>Reagin Ab [Presence] in Serum by RPR -- titer</t>
-  </si>
-  <si>
-    <t>32356-8</t>
-  </si>
-  <si>
-    <t>Yeast [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>33218-9</t>
-  </si>
-  <si>
-    <t>Bacteria [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33219-7</t>
-  </si>
-  <si>
-    <t>Epithelial cells.squamous [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33223-9</t>
-  </si>
-  <si>
-    <t>Hyaline casts [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33342-7</t>
-  </si>
-  <si>
-    <t>Epithelial cells [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33668-5</t>
-  </si>
-  <si>
-    <t>Erythrocytes [Presence] in Stool by Microscopy</t>
-  </si>
-  <si>
-    <t>33863-2</t>
-  </si>
-  <si>
-    <t>Cystatin C [Mass/volume] in Serum, Plasma or Blood</t>
-  </si>
-  <si>
-    <t>33914-3</t>
-  </si>
-  <si>
-    <t>Glomerular filtration rate/1.73 sq M.predicted by MDRD equation</t>
-  </si>
-  <si>
-    <t>34921-7</t>
-  </si>
-  <si>
-    <t>Plasmacytoid lymphocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>42524-9</t>
-  </si>
-  <si>
-    <t>Mucus [Presence] in Stool by Microscopy</t>
-  </si>
-  <si>
-    <t>43755-8</t>
-  </si>
-  <si>
-    <t>Casts [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>4548-4</t>
-  </si>
-  <si>
-    <t>Hemoglobin A1c/Hemoglobin.total in Blood</t>
-  </si>
-  <si>
-    <t>4588-0</t>
-  </si>
-  <si>
-    <t>Hemoglobin H/Hemoglobin.total in Blood</t>
-  </si>
-  <si>
-    <t>46419-8</t>
-  </si>
-  <si>
-    <t>Erythrocytes [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>46702-7</t>
-  </si>
-  <si>
-    <t>Leukocytes [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>46986-6</t>
-  </si>
-  <si>
-    <t>Cholesterol in VLDL [Mass/volume] in Serum or Plasma by calculation</t>
-  </si>
-  <si>
-    <t>47214-2</t>
-  </si>
-  <si>
-    <t>Homeostasis model assessment</t>
-  </si>
-  <si>
-    <t>49154-8</t>
-  </si>
-  <si>
-    <t>Uric acid [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>50235-1</t>
-  </si>
-  <si>
-    <t>Mucus [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>50551-1</t>
-  </si>
-  <si>
-    <t>Bilirubin [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>50555-2</t>
-  </si>
-  <si>
-    <t>Glucose [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>50558-6</t>
-  </si>
-  <si>
-    <t>Nitrite [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>50560-2</t>
-  </si>
-  <si>
-    <t>pH of Urine by Test strip</t>
-  </si>
-  <si>
-    <t>50562-8</t>
-  </si>
-  <si>
-    <t>Specific gravity of Urine by Refractometer</t>
-  </si>
-  <si>
-    <t>5176-3</t>
-  </si>
-  <si>
-    <t>Helicobacter pylori IgG Ab [Presence] in Serum</t>
-  </si>
-  <si>
-    <t>51913-2</t>
-  </si>
-  <si>
-    <t>Hepatitis A virus Ab [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5193-8</t>
-  </si>
-  <si>
-    <t>Hepatitis B virus surface Ab [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>53324-0</t>
-  </si>
-  <si>
-    <t>Spermatozoa [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>5334-8</t>
-  </si>
-  <si>
-    <t>Rubella virus IgG Ab [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>53975-9</t>
-  </si>
-  <si>
-    <t>Drug crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5403-1</t>
-  </si>
-  <si>
-    <t>Varicella zoster virus IgG Ab [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>56888-1</t>
-  </si>
-  <si>
-    <t>HIV 1 and 2 Ag and Ab panel [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5766-1</t>
-  </si>
-  <si>
-    <t>Ammonium acid urate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5770-3</t>
-  </si>
-  <si>
-    <t>5771-1</t>
-  </si>
-  <si>
-    <t>Bilirubin crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5773-7</t>
-  </si>
-  <si>
-    <t>Calcium carbonate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>57734-6</t>
-  </si>
-  <si>
-    <t>Ketones [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>5774-5</t>
-  </si>
-  <si>
-    <t>Calcium oxalate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5775-2</t>
-  </si>
-  <si>
-    <t>Calcium phosphate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>57751-0</t>
-  </si>
-  <si>
-    <t>Hemoglobin [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>5777-8</t>
-  </si>
-  <si>
-    <t>Cholesterol crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5784-4</t>
-  </si>
-  <si>
-    <t>Cystine crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5787-7</t>
-  </si>
-  <si>
-    <t>Epithelial cells [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>5788-5</t>
-  </si>
-  <si>
-    <t>Oval fat bodies [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>5792-7</t>
-  </si>
-  <si>
-    <t>5794-3</t>
-  </si>
-  <si>
-    <t>5796-8</t>
-  </si>
-  <si>
-    <t>Hyaline casts [#/area] in Urine sediment by Microscopy low power field</t>
-  </si>
-  <si>
-    <t>5797-6</t>
-  </si>
-  <si>
-    <t>5799-2</t>
-  </si>
-  <si>
-    <t>Leukocyte esterase [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>5802-4</t>
-  </si>
-  <si>
-    <t>5803-2</t>
-  </si>
-  <si>
-    <t>5813-1</t>
-  </si>
-  <si>
-    <t>Trichomonas vaginalis [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5814-9</t>
-  </si>
-  <si>
-    <t>Calcium magnesium ammonium phosphate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5817-2</t>
-  </si>
-  <si>
-    <t>Uric acid crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5821-4</t>
-  </si>
-  <si>
-    <t>Leukocytes [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>5905-5</t>
-  </si>
-  <si>
-    <t>Monocytes/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>59261-8</t>
-  </si>
-  <si>
-    <t>Hemoglobin A1c/Hemoglobin.total in Blood by IFCC protocol</t>
-  </si>
-  <si>
-    <t>60026-2</t>
-  </si>
-  <si>
-    <t>62292-8</t>
-  </si>
-  <si>
-    <t>25-hydroxyvitamin D3 [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>62487-4</t>
-  </si>
-  <si>
-    <t>6768-6</t>
-  </si>
-  <si>
-    <t>70028-6</t>
-  </si>
-  <si>
-    <t>Megakaryocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>706-2</t>
-  </si>
-  <si>
-    <t>Basophils/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>713-8</t>
-  </si>
-  <si>
-    <t>Eosinophils/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>731-0</t>
-  </si>
-  <si>
-    <t>Lymphocytes [#/volume] in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>751-8</t>
-  </si>
-  <si>
-    <t>Neutrophils [#/volume] in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>785-6</t>
-  </si>
-  <si>
-    <t>786-4</t>
-  </si>
-  <si>
-    <t>MCHC [Mass/volume] by Automated count</t>
-  </si>
-  <si>
-    <t>787-2</t>
-  </si>
-  <si>
-    <t>MCV [Entitic volume] by Automated count</t>
-  </si>
-  <si>
-    <t>788-0</t>
-  </si>
-  <si>
-    <t>Erythrocyte distribution width [Ratio] by Automated count</t>
-  </si>
-  <si>
-    <t>7962-4</t>
-  </si>
-  <si>
-    <t>Measles virus IgG Ab [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>79880-1</t>
-  </si>
-  <si>
-    <t>Vision test panel</t>
-  </si>
-  <si>
-    <t>804-5</t>
-  </si>
-  <si>
-    <t>WBC [#/volume] in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>8099-4</t>
-  </si>
-  <si>
-    <t>Thyroid peroxidase Ab [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>88112-8</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
-  </si>
-  <si>
-    <t>88293-6</t>
-  </si>
-  <si>
-    <t>Glomerular filtration rate/1.73 sq M.predicted by Creatinine-based formula (CKD-EPI 2021)</t>
-  </si>
-  <si>
-    <t>9397-1</t>
-  </si>
-  <si>
-    <t>Color of Stool</t>
-  </si>
-  <si>
-    <t>9830-1</t>
-  </si>
-  <si>
-    <t>Cholesterol/Cholesterol in HDL [Mass Ratio] in Serum or Plasma</t>
+    <t>98497-1</t>
+  </si>
+  <si>
+    <t>Visual acuity panel</t>
   </si>
   <si>
     <t>System URI</t>
@@ -3257,935 +3257,935 @@
         <v>314</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>315</v>
+        <v>105</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B146" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B147" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B148" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B149" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B150" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B151" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>327</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B152" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B153" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B154" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B155" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>335</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B156" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B157" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B158" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>341</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B159" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>343</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B160" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>345</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B161" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>347</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B162" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>349</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B163" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B164" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B165" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>357</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B167" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>361</v>
+        <v>332</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>105</v>
+        <v>401</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B190" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B191" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>406</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B192" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B193" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>410</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B195" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>414</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B196" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B197" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>418</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B198" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B199" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>422</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>424</v>
+        <v>407</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>494</v>
+        <v>520</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B250" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>523</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B251" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>525</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B252" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>527</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B253" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>529</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B254" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B255" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>535</v>
+        <v>518</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>496</v>
+        <v>541</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B261" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="B261" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="262">
@@ -4201,63 +4201,63 @@
         <v>546</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>527</v>
+        <v>547</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>498</v>
+        <v>551</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>500</v>
+        <v>553</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>552</v>
+        <v>520</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>554</v>
+        <v>545</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>558</v>
+        <v>539</v>
       </c>
     </row>
     <row r="271">
@@ -4273,31 +4273,31 @@
         <v>561</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>562</v>
+        <v>522</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>548</v>
+        <v>524</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B274" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="B274" t="s" s="2">
-        <v>565</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B275" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="B275" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="276">
@@ -4305,23 +4305,23 @@
         <v>567</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>351</v>
+        <v>568</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
     </row>
     <row r="279">
@@ -4329,31 +4329,31 @@
         <v>572</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>573</v>
+        <v>486</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B280" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="B280" t="s" s="2">
-        <v>575</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B281" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="B281" t="s" s="2">
-        <v>577</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B282" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="B282" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="283">

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -381,1435 +381,1435 @@
     <t>XR Bones.long Survey</t>
   </si>
   <si>
+    <t>19868-9</t>
+  </si>
+  <si>
+    <t>Forced vital capacity [Volume] Respiratory system by Spirometry</t>
+  </si>
+  <si>
+    <t>20150-9</t>
+  </si>
+  <si>
+    <t>FEV1</t>
+  </si>
+  <si>
+    <t>19926-5</t>
+  </si>
+  <si>
+    <t>FEV1/FVC</t>
+  </si>
+  <si>
+    <t>5671-3</t>
+  </si>
+  <si>
+    <t>Lead [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5676-2</t>
+  </si>
+  <si>
+    <t>Lead [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>23749-5</t>
+  </si>
+  <si>
+    <t>Lead [Mass/volume] in Specimen</t>
+  </si>
+  <si>
+    <t>11212-8</t>
+  </si>
+  <si>
+    <t>Coproporphyrin [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>11215-1</t>
+  </si>
+  <si>
+    <t>Aminolevulinic acid [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>36643-5</t>
+  </si>
+  <si>
+    <t>XR Chest 2 Views</t>
+  </si>
+  <si>
+    <t>24648-8</t>
+  </si>
+  <si>
+    <t>XR Chest PA upright</t>
+  </si>
+  <si>
+    <t>2324-2</t>
+  </si>
+  <si>
+    <t>Gamma glutamyltransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>6709-0</t>
+  </si>
+  <si>
+    <t>Hippurate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>2725-0</t>
+  </si>
+  <si>
+    <t>p-Methylhippurate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>13000-5</t>
+  </si>
+  <si>
+    <t>Mandelate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>3041-1</t>
+  </si>
+  <si>
+    <t>Trichloroacetate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>31170-4</t>
+  </si>
+  <si>
+    <t>2,5-Hexanedione [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>2758-1</t>
+  </si>
+  <si>
+    <t>Phenol [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>12543-5</t>
+  </si>
+  <si>
+    <t>Methylformamide [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>12533-6</t>
+  </si>
+  <si>
+    <t>TTCA [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5586-3</t>
+  </si>
+  <si>
+    <t>Arsenic [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5609-3</t>
+  </si>
+  <si>
+    <t>Cadmium [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5611-9</t>
+  </si>
+  <si>
+    <t>Cadmium [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>13471-8</t>
+  </si>
+  <si>
+    <t>Cadmium/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
+    <t>5622-6</t>
+  </si>
+  <si>
+    <t>Chromium [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5623-4</t>
+  </si>
+  <si>
+    <t>Chromium [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>13464-3</t>
+  </si>
+  <si>
+    <t>Chromium/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
+    <t>14099-6</t>
+  </si>
+  <si>
+    <t>Nickel [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5685-3</t>
+  </si>
+  <si>
+    <t>Mercury [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5689-5</t>
+  </si>
+  <si>
+    <t>Mercury [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>72665-3</t>
+  </si>
+  <si>
+    <t>trans,trans-Muconic acid [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>10913-2</t>
+  </si>
+  <si>
+    <t>4,4'-Methylenebis(2-chloroaniline) [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5653-1</t>
+  </si>
+  <si>
+    <t>Formaldehyde [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>10909-0</t>
+  </si>
+  <si>
+    <t>Benzidine [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5681-2</t>
+  </si>
+  <si>
+    <t>Manganese [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5683-8</t>
+  </si>
+  <si>
+    <t>Manganese [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>42221-2</t>
+  </si>
+  <si>
+    <t>Manganese [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>34304-6</t>
+  </si>
+  <si>
+    <t>Fluoride [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>2777-1</t>
+  </si>
+  <si>
+    <t>Phosphate [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>24829-4</t>
+  </si>
+  <si>
+    <t>XR Mandible Views</t>
+  </si>
+  <si>
+    <t>9827-7</t>
+  </si>
+  <si>
+    <t>Paraquat [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>60090-8</t>
+  </si>
+  <si>
+    <t>Indium [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5665-5</t>
+  </si>
+  <si>
+    <t>Indium [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5627-5</t>
+  </si>
+  <si>
+    <t>Cobalt [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5625-9</t>
+  </si>
+  <si>
+    <t>Cobalt [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>1984-4</t>
+  </si>
+  <si>
+    <t>Bromide [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1985-1</t>
+  </si>
+  <si>
+    <t>Bromide [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>1709-5</t>
+  </si>
+  <si>
+    <t>Acetylcholinesterase [Enzymatic activity/volume] in Red Blood Cells</t>
+  </si>
+  <si>
+    <t>2098-2</t>
+  </si>
+  <si>
+    <t>Cholinesterase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>43371-4</t>
+  </si>
+  <si>
+    <t>Salmonella and Shigella [Presence] in Stool by Culture</t>
+  </si>
+  <si>
+    <t>19266-6</t>
+  </si>
+  <si>
+    <t>Amphetamines [Presence] in Urine by Screening test</t>
+  </si>
+  <si>
+    <t>19299-7</t>
+  </si>
+  <si>
+    <t>Opiates [Presence] in Urine by Screening test</t>
+  </si>
+  <si>
+    <t>19283-1</t>
+  </si>
+  <si>
+    <t>Benzodiazepines [Presence] in Urine by Screening test</t>
+  </si>
+  <si>
+    <t>19501-6</t>
+  </si>
+  <si>
+    <t>Ketamine [Presence] in Urine by Screening test</t>
+  </si>
+  <si>
+    <t>19571-9</t>
+  </si>
+  <si>
+    <t>MDMA [Presence] in Urine by Screening test</t>
+  </si>
+  <si>
+    <t>19177-5</t>
+  </si>
+  <si>
+    <t>Alpha-1-fetoprotein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2039-6</t>
+  </si>
+  <si>
+    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2857-1</t>
+  </si>
+  <si>
+    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>19199-9</t>
+  </si>
+  <si>
+    <t>10886-0</t>
+  </si>
+  <si>
+    <t>Prostate specific Ag.free [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>97149-9</t>
+  </si>
+  <si>
+    <t>[-2]pro-prostate specific antigen [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>97150-7</t>
+  </si>
+  <si>
+    <t>Prostate Health Index in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>10334-1</t>
+  </si>
+  <si>
+    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>83082-8</t>
+  </si>
+  <si>
+    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>83085-1</t>
+  </si>
+  <si>
+    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>24108-3</t>
+  </si>
+  <si>
+    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>83084-4</t>
+  </si>
+  <si>
+    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>83083-6</t>
+  </si>
+  <si>
+    <t>Cancer Ag 15-3 [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>83112-3</t>
+  </si>
+  <si>
+    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>1834-1</t>
+  </si>
+  <si>
+    <t>9679-2</t>
+  </si>
+  <si>
+    <t>Squamous cell carcinoma Ag [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>19113-0</t>
+  </si>
+  <si>
+    <t>IgE [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>9633-9</t>
+  </si>
+  <si>
+    <t>Epstein Barr virus VCA IgA Ab [Presence] in Serum</t>
+  </si>
+  <si>
+    <t>10835-7</t>
+  </si>
+  <si>
+    <t>Lipoprotein A [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1869-7</t>
+  </si>
+  <si>
+    <t>Apolipoprotein A-I [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1884-6</t>
+  </si>
+  <si>
+    <t>Apolipoprotein B [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>33762-6</t>
+  </si>
+  <si>
+    <t>Natriuretic peptide.proB-type N-terminal [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>42254-3</t>
+  </si>
+  <si>
+    <t>Nuclear Ab [Presence] in Serum by Immunofluorescence</t>
+  </si>
+  <si>
+    <t>11572-5</t>
+  </si>
+  <si>
+    <t>Rheumatoid factor [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>25390-6</t>
+  </si>
+  <si>
+    <t>CYFRA 21-1 [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>24606-6</t>
+  </si>
+  <si>
+    <t>MG Breast Screening</t>
+  </si>
+  <si>
+    <t>103892-6</t>
+  </si>
+  <si>
+    <t>DBT Brst Screening</t>
+  </si>
+  <si>
+    <t>24590-2</t>
+  </si>
+  <si>
+    <t>MR Brain</t>
+  </si>
+  <si>
+    <t>79086-5</t>
+  </si>
+  <si>
+    <t>CT Chest Screening WO contr</t>
+  </si>
+  <si>
+    <t>87279-6</t>
+  </si>
+  <si>
+    <t>CT Chest Screening</t>
+  </si>
+  <si>
+    <t>81555-5</t>
+  </si>
+  <si>
+    <t>PT+CT Whole body Tum loc W 18F-FDG IV</t>
+  </si>
+  <si>
+    <t>79073-3</t>
+  </si>
+  <si>
+    <t>CTA Hrt+CA W contr IV</t>
+  </si>
+  <si>
+    <t>28014-9</t>
+  </si>
+  <si>
+    <t>EGD Study</t>
+  </si>
+  <si>
+    <t>28023-0</t>
+  </si>
+  <si>
+    <t>Colonoscopy Study</t>
+  </si>
+  <si>
+    <t>24558-9</t>
+  </si>
+  <si>
+    <t>Ultrasound of abdomen study</t>
+  </si>
+  <si>
+    <t>24616-5</t>
+  </si>
+  <si>
+    <t>US Carotid aa</t>
+  </si>
+  <si>
+    <t>25010-0</t>
+  </si>
+  <si>
+    <t>US Thyroid</t>
+  </si>
+  <si>
+    <t>38268-9</t>
+  </si>
+  <si>
+    <t>DXA Skeletal Sys Views for BMD</t>
+  </si>
+  <si>
+    <t>13046-8</t>
+  </si>
+  <si>
+    <t>Atypical lymphocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>13047-6</t>
+  </si>
+  <si>
+    <t>Plasma cells/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>19048-8</t>
+  </si>
+  <si>
+    <t>Erythroblasts/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>26446-5</t>
+  </si>
+  <si>
+    <t>Blasts/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26450-7</t>
+  </si>
+  <si>
+    <t>Eosinophils/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26464-8</t>
+  </si>
+  <si>
+    <t>26478-8</t>
+  </si>
+  <si>
+    <t>Lymphocytes/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26485-3</t>
+  </si>
+  <si>
+    <t>Monocytes/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26498-6</t>
+  </si>
+  <si>
+    <t>Myelocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26505-8</t>
+  </si>
+  <si>
+    <t>Hypersegmented neutrophils/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26508-2</t>
+  </si>
+  <si>
+    <t>Neutrophils/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>26511-6</t>
+  </si>
+  <si>
+    <t>Neutrophils.segmented/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26515-7</t>
+  </si>
+  <si>
+    <t>Platelets [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>26524-9</t>
+  </si>
+  <si>
+    <t>Promyelocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>28539-5</t>
+  </si>
+  <si>
+    <t>MCH [Entitic mass] by Automated count</t>
+  </si>
+  <si>
+    <t>28541-1</t>
+  </si>
+  <si>
+    <t>Metamyelocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30180-4</t>
+  </si>
+  <si>
+    <t>Basophils/100 leukocytes in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>30413-9</t>
+  </si>
+  <si>
+    <t>Abnormal lymphocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30428-7</t>
+  </si>
+  <si>
+    <t>MCV [Entitic volume] by calculation</t>
+  </si>
+  <si>
+    <t>30441-0</t>
+  </si>
+  <si>
+    <t>Abnormal monocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30466-7</t>
+  </si>
+  <si>
+    <t>Promonocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>34921-7</t>
+  </si>
+  <si>
+    <t>Plasmacytoid lymphocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>5905-5</t>
+  </si>
+  <si>
+    <t>Monocytes/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>70028-6</t>
+  </si>
+  <si>
+    <t>Megakaryocytes/100 leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>706-2</t>
+  </si>
+  <si>
+    <t>Basophils/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>713-8</t>
+  </si>
+  <si>
+    <t>Eosinophils/100 leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>731-0</t>
+  </si>
+  <si>
+    <t>Lymphocytes [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>751-8</t>
+  </si>
+  <si>
+    <t>Neutrophils [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>785-6</t>
+  </si>
+  <si>
+    <t>786-4</t>
+  </si>
+  <si>
+    <t>MCHC [Mass/volume] by Automated count</t>
+  </si>
+  <si>
+    <t>787-2</t>
+  </si>
+  <si>
+    <t>MCV [Entitic volume] by Automated count</t>
+  </si>
+  <si>
+    <t>788-0</t>
+  </si>
+  <si>
+    <t>Erythrocyte distribution width [Ratio] by Automated count</t>
+  </si>
+  <si>
+    <t>804-5</t>
+  </si>
+  <si>
+    <t>WBC [#/volume] in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>17861-6</t>
+  </si>
+  <si>
+    <t>Calcium [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>20448-7</t>
+  </si>
+  <si>
+    <t>Insulin [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2428-1</t>
+  </si>
+  <si>
+    <t>Homocysteine [Moles/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>30522-7</t>
+  </si>
+  <si>
+    <t>C reactive protein [Mass/volume] in Serum or Plasma by High sensitivity method</t>
+  </si>
+  <si>
+    <t>3084-1</t>
+  </si>
+  <si>
+    <t>Uric acid [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>33863-2</t>
+  </si>
+  <si>
+    <t>Cystatin C [Mass/volume] in Serum, Plasma or Blood</t>
+  </si>
+  <si>
+    <t>33914-3</t>
+  </si>
+  <si>
+    <t>Glomerular filtration rate/1.73 sq M.predicted by MDRD equation</t>
+  </si>
+  <si>
+    <t>4548-4</t>
+  </si>
+  <si>
+    <t>Hemoglobin A1c/Hemoglobin.total in Blood</t>
+  </si>
+  <si>
+    <t>47214-2</t>
+  </si>
+  <si>
+    <t>Homeostasis model assessment</t>
+  </si>
+  <si>
+    <t>49154-8</t>
+  </si>
+  <si>
+    <t>Uric acid [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>59261-8</t>
+  </si>
+  <si>
+    <t>Hemoglobin A1c/Hemoglobin.total in Blood by IFCC protocol</t>
+  </si>
+  <si>
+    <t>98979-8</t>
+  </si>
+  <si>
+    <t>Glomerular filtration rate [Volume Rate/Area] in Serum, Plasma or Blood by Creatinine-based formula (CKD-EPI 2021)/1.73 sq M</t>
+  </si>
+  <si>
+    <t>10834-0</t>
+  </si>
+  <si>
+    <t>Globulin [Mass/volume] in Serum or Plasma by calculation</t>
+  </si>
+  <si>
+    <t>14390-9</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
+  </si>
+  <si>
+    <t>14409-7</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
+  </si>
+  <si>
+    <t>1742-6</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1744-2</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+  </si>
+  <si>
+    <t>1751-7</t>
+  </si>
+  <si>
+    <t>Albumin [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1759-0</t>
+  </si>
+  <si>
+    <t>Albumin/Globulin [Mass Ratio] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1783-0</t>
+  </si>
+  <si>
+    <t>Alkaline phosphatase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1798-8</t>
+  </si>
+  <si>
+    <t>Amylase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1920-8</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1968-7</t>
+  </si>
+  <si>
+    <t>Bilirubin.direct [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1975-2</t>
+  </si>
+  <si>
+    <t>Bilirubin.total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2532-0</t>
+  </si>
+  <si>
+    <t>Lactate dehydrogenase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2885-2</t>
+  </si>
+  <si>
+    <t>Protein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3040-3</t>
+  </si>
+  <si>
+    <t>Lipase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>6768-6</t>
+  </si>
+  <si>
+    <t>88112-8</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+  </si>
+  <si>
+    <t>46986-6</t>
+  </si>
+  <si>
+    <t>Cholesterol in VLDL [Mass/volume] in Serum or Plasma by calculation</t>
+  </si>
+  <si>
+    <t>9830-1</t>
+  </si>
+  <si>
+    <t>Cholesterol/Cholesterol in HDL [Mass Ratio] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2132-9</t>
+  </si>
+  <si>
+    <t>Cobalamin (Vitamin B12) [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2284-8</t>
+  </si>
+  <si>
+    <t>Folate [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3016-3</t>
+  </si>
+  <si>
+    <t>Thyrotropin [Units/volume] in Serum or Plasma by 3rd IS</t>
+  </si>
+  <si>
+    <t>3026-2</t>
+  </si>
+  <si>
+    <t>Thyroxine (T4) total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3051-0</t>
+  </si>
+  <si>
+    <t>Triiodothyronine (T3) free [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3053-6</t>
+  </si>
+  <si>
+    <t>Triiodothyronine (T3) total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>62292-8</t>
+  </si>
+  <si>
+    <t>25-hydroxyvitamin D3 [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>8099-4</t>
+  </si>
+  <si>
+    <t>Thyroid peroxidase Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>13950-1</t>
+  </si>
+  <si>
+    <t>Hepatitis A virus IgM Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>13952-7</t>
+  </si>
+  <si>
+    <t>Hepatitis B virus core Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>17780-8</t>
+  </si>
+  <si>
+    <t>Helicobacter pylori Ag [Presence] in Stool</t>
+  </si>
+  <si>
+    <t>20507-0</t>
+  </si>
+  <si>
+    <t>Reagin Ab [Presence] in Serum by RPR</t>
+  </si>
+  <si>
+    <t>21440-3</t>
+  </si>
+  <si>
+    <t>Human papilloma virus 16+18+31+33+35+45+51+52+56 DNA [Presence] in Cervix by Probe</t>
+  </si>
+  <si>
+    <t>22322-2</t>
+  </si>
+  <si>
+    <t>Hepatitis B virus surface Ab [Units/volume] in Serum</t>
+  </si>
+  <si>
+    <t>24110-9</t>
+  </si>
+  <si>
+    <t>Treponema pallidum Ab [Presence] in Serum by Immunoassay</t>
+  </si>
+  <si>
+    <t>29771-3</t>
+  </si>
+  <si>
+    <t>Hemoglobin.occult [Mass/volume] in Stool by Immunochemical method</t>
+  </si>
+  <si>
+    <t>31147-2</t>
+  </si>
+  <si>
+    <t>Reagin Ab [Presence] in Serum by RPR -- titer</t>
+  </si>
+  <si>
+    <t>5176-3</t>
+  </si>
+  <si>
+    <t>Helicobacter pylori IgG Ab [Presence] in Serum</t>
+  </si>
+  <si>
+    <t>51913-2</t>
+  </si>
+  <si>
+    <t>Hepatitis A virus Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5193-8</t>
+  </si>
+  <si>
+    <t>Hepatitis B virus surface Ab [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5334-8</t>
+  </si>
+  <si>
+    <t>Rubella virus IgG Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5403-1</t>
+  </si>
+  <si>
+    <t>Varicella zoster virus IgG Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>56888-1</t>
+  </si>
+  <si>
+    <t>HIV 1 and 2 Ag and Ab panel [Presence] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>7962-4</t>
+  </si>
+  <si>
+    <t>Measles virus IgG Ab [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>11218-5</t>
+  </si>
+  <si>
+    <t>Microalbumin [Mass/volume] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>11277-1</t>
+  </si>
+  <si>
+    <t>Epithelial cells.squamous [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>12453-7</t>
+  </si>
+  <si>
+    <t>Amorphous phosphate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>12454-5</t>
+  </si>
+  <si>
+    <t>Amorphous urate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>13658-0</t>
+  </si>
+  <si>
+    <t>Urobilinogen [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>13945-1</t>
+  </si>
+  <si>
+    <t>Erythrocytes [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>20456-0</t>
+  </si>
+  <si>
+    <t>Fungi yeast-like [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>20621-9</t>
+  </si>
+  <si>
+    <t>Albumin/Creatinine [Ratio] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>20627-6</t>
+  </si>
+  <si>
+    <t>Color of Urine</t>
+  </si>
+  <si>
+    <t>25145-4</t>
+  </si>
+  <si>
+    <t>Bacteria [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>30004-6</t>
+  </si>
+  <si>
+    <t>Creatinine [Mass/volume] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>32356-8</t>
+  </si>
+  <si>
+    <t>Yeast [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>33218-9</t>
+  </si>
+  <si>
+    <t>Bacteria [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33219-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells.squamous [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33223-9</t>
+  </si>
+  <si>
+    <t>Hyaline casts [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>33342-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>43755-8</t>
+  </si>
+  <si>
+    <t>Casts [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>46419-8</t>
+  </si>
+  <si>
+    <t>Erythrocytes [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>46702-7</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>50235-1</t>
+  </si>
+  <si>
+    <t>Mucus [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>50551-1</t>
+  </si>
+  <si>
+    <t>Bilirubin [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50555-2</t>
+  </si>
+  <si>
+    <t>Glucose [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50558-6</t>
+  </si>
+  <si>
+    <t>Nitrite [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50560-2</t>
+  </si>
+  <si>
+    <t>pH of Urine by Test strip</t>
+  </si>
+  <si>
+    <t>50562-8</t>
+  </si>
+  <si>
+    <t>Specific gravity of Urine by Refractometer</t>
+  </si>
+  <si>
+    <t>53324-0</t>
+  </si>
+  <si>
+    <t>Spermatozoa [#/volume] in Urine sediment by Automated count</t>
+  </si>
+  <si>
+    <t>53975-9</t>
+  </si>
+  <si>
+    <t>Drug crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5766-1</t>
+  </si>
+  <si>
+    <t>Ammonium acid urate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5770-3</t>
+  </si>
+  <si>
+    <t>5771-1</t>
+  </si>
+  <si>
+    <t>Bilirubin crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5773-7</t>
+  </si>
+  <si>
+    <t>Calcium carbonate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>57734-6</t>
+  </si>
+  <si>
+    <t>Ketones [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5774-5</t>
+  </si>
+  <si>
+    <t>Calcium oxalate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5775-2</t>
+  </si>
+  <si>
+    <t>Calcium phosphate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>57751-0</t>
+  </si>
+  <si>
+    <t>Hemoglobin [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5777-8</t>
+  </si>
+  <si>
+    <t>Cholesterol crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5784-4</t>
+  </si>
+  <si>
+    <t>Cystine crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5787-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>5788-5</t>
+  </si>
+  <si>
+    <t>Oval fat bodies [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>5792-7</t>
+  </si>
+  <si>
+    <t>5794-3</t>
+  </si>
+  <si>
+    <t>5796-8</t>
+  </si>
+  <si>
+    <t>Hyaline casts [#/area] in Urine sediment by Microscopy low power field</t>
+  </si>
+  <si>
+    <t>5797-6</t>
+  </si>
+  <si>
+    <t>5799-2</t>
+  </si>
+  <si>
+    <t>Leukocyte esterase [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5802-4</t>
+  </si>
+  <si>
+    <t>5803-2</t>
+  </si>
+  <si>
+    <t>5813-1</t>
+  </si>
+  <si>
+    <t>Trichomonas vaginalis [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5814-9</t>
+  </si>
+  <si>
+    <t>Calcium magnesium ammonium phosphate crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5817-2</t>
+  </si>
+  <si>
+    <t>Uric acid crystals [Presence] in Urine sediment</t>
+  </si>
+  <si>
+    <t>5821-4</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>60026-2</t>
+  </si>
+  <si>
+    <t>62487-4</t>
+  </si>
+  <si>
+    <t>13705-9</t>
+  </si>
+  <si>
+    <t>Albumin/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
+    <t>14957-5</t>
+  </si>
+  <si>
+    <t>Microalbumin [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>1988-5</t>
+  </si>
+  <si>
+    <t>C reactive protein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2161-8</t>
+  </si>
+  <si>
+    <t>Creatinine [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>4588-0</t>
+  </si>
+  <si>
+    <t>Hemoglobin H/Hemoglobin.total in Blood</t>
+  </si>
+  <si>
+    <t>10701-1</t>
+  </si>
+  <si>
+    <t>Ova and parasites [Presence] in Stool by Concentration method</t>
+  </si>
+  <si>
+    <t>10704-5</t>
+  </si>
+  <si>
+    <t>Ova and parasites [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>13655-6</t>
+  </si>
+  <si>
+    <t>Leukocytes [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>2335-8</t>
+  </si>
+  <si>
+    <t>Hemoglobin [Presence] in Stool</t>
+  </si>
+  <si>
+    <t>33668-5</t>
+  </si>
+  <si>
+    <t>Erythrocytes [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>42524-9</t>
+  </si>
+  <si>
+    <t>Mucus [Presence] in Stool by Microscopy</t>
+  </si>
+  <si>
+    <t>9397-1</t>
+  </si>
+  <si>
+    <t>Color of Stool</t>
+  </si>
+  <si>
     <t>19876-2</t>
   </si>
   <si>
     <t>Forced vital capacity [Volume] Respiratory system by Spirometry --pre bronchodilation</t>
-  </si>
-  <si>
-    <t>20150-9</t>
-  </si>
-  <si>
-    <t>FEV1</t>
-  </si>
-  <si>
-    <t>19926-5</t>
-  </si>
-  <si>
-    <t>FEV1/FVC</t>
-  </si>
-  <si>
-    <t>5671-3</t>
-  </si>
-  <si>
-    <t>Lead [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5676-2</t>
-  </si>
-  <si>
-    <t>Lead [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>23749-5</t>
-  </si>
-  <si>
-    <t>Lead [Mass/volume] in Specimen</t>
-  </si>
-  <si>
-    <t>11212-8</t>
-  </si>
-  <si>
-    <t>Coproporphyrin [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>11215-1</t>
-  </si>
-  <si>
-    <t>Aminolevulinic acid [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>36643-5</t>
-  </si>
-  <si>
-    <t>XR Chest 2 Views</t>
-  </si>
-  <si>
-    <t>24648-8</t>
-  </si>
-  <si>
-    <t>XR Chest PA upright</t>
-  </si>
-  <si>
-    <t>2324-2</t>
-  </si>
-  <si>
-    <t>Gamma glutamyltransferase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>6709-0</t>
-  </si>
-  <si>
-    <t>Hippurate [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>2725-0</t>
-  </si>
-  <si>
-    <t>p-Methylhippurate [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>13000-5</t>
-  </si>
-  <si>
-    <t>Mandelate [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>3041-1</t>
-  </si>
-  <si>
-    <t>Trichloroacetate [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>31170-4</t>
-  </si>
-  <si>
-    <t>2,5-Hexanedione [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>2758-1</t>
-  </si>
-  <si>
-    <t>Phenol [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>12543-5</t>
-  </si>
-  <si>
-    <t>Methylformamide [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>12533-6</t>
-  </si>
-  <si>
-    <t>TTCA [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5586-3</t>
-  </si>
-  <si>
-    <t>Arsenic [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5609-3</t>
-  </si>
-  <si>
-    <t>Cadmium [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5611-9</t>
-  </si>
-  <si>
-    <t>Cadmium [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>13471-8</t>
-  </si>
-  <si>
-    <t>Cadmium/Creatinine [Mass Ratio] in Urine</t>
-  </si>
-  <si>
-    <t>5622-6</t>
-  </si>
-  <si>
-    <t>Chromium [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5623-4</t>
-  </si>
-  <si>
-    <t>Chromium [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>13464-3</t>
-  </si>
-  <si>
-    <t>Chromium/Creatinine [Mass Ratio] in Urine</t>
-  </si>
-  <si>
-    <t>14099-6</t>
-  </si>
-  <si>
-    <t>Nickel [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5685-3</t>
-  </si>
-  <si>
-    <t>Mercury [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5689-5</t>
-  </si>
-  <si>
-    <t>Mercury [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>72665-3</t>
-  </si>
-  <si>
-    <t>trans,trans-Muconic acid [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>10913-2</t>
-  </si>
-  <si>
-    <t>4,4'-Methylenebis(2-chloroaniline) [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5653-1</t>
-  </si>
-  <si>
-    <t>Formaldehyde [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>10909-0</t>
-  </si>
-  <si>
-    <t>Benzidine [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5681-2</t>
-  </si>
-  <si>
-    <t>Manganese [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5683-8</t>
-  </si>
-  <si>
-    <t>Manganese [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>42221-2</t>
-  </si>
-  <si>
-    <t>Manganese [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>34304-6</t>
-  </si>
-  <si>
-    <t>Fluoride [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>2777-1</t>
-  </si>
-  <si>
-    <t>Phosphate [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>24829-4</t>
-  </si>
-  <si>
-    <t>XR Mandible Views</t>
-  </si>
-  <si>
-    <t>9827-7</t>
-  </si>
-  <si>
-    <t>Paraquat [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>60090-8</t>
-  </si>
-  <si>
-    <t>Indium [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5665-5</t>
-  </si>
-  <si>
-    <t>Indium [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5627-5</t>
-  </si>
-  <si>
-    <t>Cobalt [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5625-9</t>
-  </si>
-  <si>
-    <t>Cobalt [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>1984-4</t>
-  </si>
-  <si>
-    <t>Bromide [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1985-1</t>
-  </si>
-  <si>
-    <t>Bromide [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>1709-5</t>
-  </si>
-  <si>
-    <t>Acetylcholinesterase [Enzymatic activity/volume] in Red Blood Cells</t>
-  </si>
-  <si>
-    <t>2098-2</t>
-  </si>
-  <si>
-    <t>Cholinesterase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>43371-4</t>
-  </si>
-  <si>
-    <t>Salmonella and Shigella [Presence] in Stool by Culture</t>
-  </si>
-  <si>
-    <t>19266-6</t>
-  </si>
-  <si>
-    <t>Amphetamines [Presence] in Urine by Screening test</t>
-  </si>
-  <si>
-    <t>19299-7</t>
-  </si>
-  <si>
-    <t>Opiates [Presence] in Urine by Screening test</t>
-  </si>
-  <si>
-    <t>19283-1</t>
-  </si>
-  <si>
-    <t>Benzodiazepines [Presence] in Urine by Screening test</t>
-  </si>
-  <si>
-    <t>19501-6</t>
-  </si>
-  <si>
-    <t>Ketamine [Presence] in Urine by Screening test</t>
-  </si>
-  <si>
-    <t>19571-9</t>
-  </si>
-  <si>
-    <t>MDMA [Presence] in Urine by Screening test</t>
-  </si>
-  <si>
-    <t>19177-5</t>
-  </si>
-  <si>
-    <t>Alpha-1-fetoprotein [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2039-6</t>
-  </si>
-  <si>
-    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2857-1</t>
-  </si>
-  <si>
-    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>19199-9</t>
-  </si>
-  <si>
-    <t>10886-0</t>
-  </si>
-  <si>
-    <t>Prostate specific Ag.free [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>97149-9</t>
-  </si>
-  <si>
-    <t>[-2]pro-prostate specific antigen [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>97150-7</t>
-  </si>
-  <si>
-    <t>Prostate Health Index in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>10334-1</t>
-  </si>
-  <si>
-    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>83082-8</t>
-  </si>
-  <si>
-    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>83085-1</t>
-  </si>
-  <si>
-    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>24108-3</t>
-  </si>
-  <si>
-    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>83084-4</t>
-  </si>
-  <si>
-    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>83083-6</t>
-  </si>
-  <si>
-    <t>Cancer Ag 15-3 [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>83112-3</t>
-  </si>
-  <si>
-    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>1834-1</t>
-  </si>
-  <si>
-    <t>9679-2</t>
-  </si>
-  <si>
-    <t>Squamous cell carcinoma Ag [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>19113-0</t>
-  </si>
-  <si>
-    <t>IgE [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>9633-9</t>
-  </si>
-  <si>
-    <t>Epstein Barr virus VCA IgA Ab [Presence] in Serum</t>
-  </si>
-  <si>
-    <t>10835-7</t>
-  </si>
-  <si>
-    <t>Lipoprotein A [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1869-7</t>
-  </si>
-  <si>
-    <t>Apolipoprotein A-I [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1884-6</t>
-  </si>
-  <si>
-    <t>Apolipoprotein B [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>33762-6</t>
-  </si>
-  <si>
-    <t>Natriuretic peptide.proB-type N-terminal [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>42254-3</t>
-  </si>
-  <si>
-    <t>Nuclear Ab [Presence] in Serum by Immunofluorescence</t>
-  </si>
-  <si>
-    <t>11572-5</t>
-  </si>
-  <si>
-    <t>Rheumatoid factor [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>25390-6</t>
-  </si>
-  <si>
-    <t>CYFRA 21-1 [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>24606-6</t>
-  </si>
-  <si>
-    <t>MG Breast Screening</t>
-  </si>
-  <si>
-    <t>103892-6</t>
-  </si>
-  <si>
-    <t>DBT Brst Screening</t>
-  </si>
-  <si>
-    <t>24590-2</t>
-  </si>
-  <si>
-    <t>MR Brain</t>
-  </si>
-  <si>
-    <t>79086-5</t>
-  </si>
-  <si>
-    <t>CT Chest Screening WO contr</t>
-  </si>
-  <si>
-    <t>87279-6</t>
-  </si>
-  <si>
-    <t>CT Chest Screening</t>
-  </si>
-  <si>
-    <t>81555-5</t>
-  </si>
-  <si>
-    <t>PT+CT Whole body Tum loc W 18F-FDG IV</t>
-  </si>
-  <si>
-    <t>79073-3</t>
-  </si>
-  <si>
-    <t>CTA Hrt+CA W contr IV</t>
-  </si>
-  <si>
-    <t>28014-9</t>
-  </si>
-  <si>
-    <t>EGD Study</t>
-  </si>
-  <si>
-    <t>28023-0</t>
-  </si>
-  <si>
-    <t>Colonoscopy Study</t>
-  </si>
-  <si>
-    <t>24558-9</t>
-  </si>
-  <si>
-    <t>Ultrasound of abdomen study</t>
-  </si>
-  <si>
-    <t>24616-5</t>
-  </si>
-  <si>
-    <t>US Carotid aa</t>
-  </si>
-  <si>
-    <t>25010-0</t>
-  </si>
-  <si>
-    <t>US Thyroid</t>
-  </si>
-  <si>
-    <t>38268-9</t>
-  </si>
-  <si>
-    <t>DXA Skeletal Sys Views for BMD</t>
-  </si>
-  <si>
-    <t>13046-8</t>
-  </si>
-  <si>
-    <t>Atypical lymphocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>13047-6</t>
-  </si>
-  <si>
-    <t>Plasma cells/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>19048-8</t>
-  </si>
-  <si>
-    <t>Erythroblasts/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>26446-5</t>
-  </si>
-  <si>
-    <t>Blasts/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26450-7</t>
-  </si>
-  <si>
-    <t>Eosinophils/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26464-8</t>
-  </si>
-  <si>
-    <t>26478-8</t>
-  </si>
-  <si>
-    <t>Lymphocytes/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26485-3</t>
-  </si>
-  <si>
-    <t>Monocytes/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26498-6</t>
-  </si>
-  <si>
-    <t>Myelocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26505-8</t>
-  </si>
-  <si>
-    <t>Hypersegmented neutrophils/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26508-2</t>
-  </si>
-  <si>
-    <t>Neutrophils/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26511-6</t>
-  </si>
-  <si>
-    <t>Neutrophils.segmented/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26515-7</t>
-  </si>
-  <si>
-    <t>Platelets [#/volume] in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>26524-9</t>
-  </si>
-  <si>
-    <t>Promyelocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>28539-5</t>
-  </si>
-  <si>
-    <t>MCH [Entitic mass] by Automated count</t>
-  </si>
-  <si>
-    <t>28541-1</t>
-  </si>
-  <si>
-    <t>Metamyelocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>30180-4</t>
-  </si>
-  <si>
-    <t>Basophils/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>30413-9</t>
-  </si>
-  <si>
-    <t>Abnormal lymphocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>30428-7</t>
-  </si>
-  <si>
-    <t>MCV [Entitic volume] by calculation</t>
-  </si>
-  <si>
-    <t>30441-0</t>
-  </si>
-  <si>
-    <t>Abnormal monocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>30466-7</t>
-  </si>
-  <si>
-    <t>Promonocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>34921-7</t>
-  </si>
-  <si>
-    <t>Plasmacytoid lymphocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>5905-5</t>
-  </si>
-  <si>
-    <t>Monocytes/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>70028-6</t>
-  </si>
-  <si>
-    <t>Megakaryocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>706-2</t>
-  </si>
-  <si>
-    <t>Basophils/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>713-8</t>
-  </si>
-  <si>
-    <t>Eosinophils/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>731-0</t>
-  </si>
-  <si>
-    <t>Lymphocytes [#/volume] in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>751-8</t>
-  </si>
-  <si>
-    <t>Neutrophils [#/volume] in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>785-6</t>
-  </si>
-  <si>
-    <t>786-4</t>
-  </si>
-  <si>
-    <t>MCHC [Mass/volume] by Automated count</t>
-  </si>
-  <si>
-    <t>787-2</t>
-  </si>
-  <si>
-    <t>MCV [Entitic volume] by Automated count</t>
-  </si>
-  <si>
-    <t>788-0</t>
-  </si>
-  <si>
-    <t>Erythrocyte distribution width [Ratio] by Automated count</t>
-  </si>
-  <si>
-    <t>804-5</t>
-  </si>
-  <si>
-    <t>WBC [#/volume] in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>17861-6</t>
-  </si>
-  <si>
-    <t>Calcium [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>20448-7</t>
-  </si>
-  <si>
-    <t>Insulin [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2428-1</t>
-  </si>
-  <si>
-    <t>Homocysteine [Moles/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>30522-7</t>
-  </si>
-  <si>
-    <t>C reactive protein [Mass/volume] in Serum or Plasma by High sensitivity method</t>
-  </si>
-  <si>
-    <t>3084-1</t>
-  </si>
-  <si>
-    <t>Uric acid [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>33863-2</t>
-  </si>
-  <si>
-    <t>Cystatin C [Mass/volume] in Serum, Plasma or Blood</t>
-  </si>
-  <si>
-    <t>33914-3</t>
-  </si>
-  <si>
-    <t>Glomerular filtration rate/1.73 sq M.predicted by MDRD equation</t>
-  </si>
-  <si>
-    <t>4548-4</t>
-  </si>
-  <si>
-    <t>Hemoglobin A1c/Hemoglobin.total in Blood</t>
-  </si>
-  <si>
-    <t>47214-2</t>
-  </si>
-  <si>
-    <t>Homeostasis model assessment</t>
-  </si>
-  <si>
-    <t>49154-8</t>
-  </si>
-  <si>
-    <t>Uric acid [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>59261-8</t>
-  </si>
-  <si>
-    <t>Hemoglobin A1c/Hemoglobin.total in Blood by IFCC protocol</t>
-  </si>
-  <si>
-    <t>98979-8</t>
-  </si>
-  <si>
-    <t>Glomerular filtration rate [Volume Rate/Area] in Serum, Plasma or Blood by Creatinine-based formula (CKD-EPI 2021)/1.73 sq M</t>
-  </si>
-  <si>
-    <t>10834-0</t>
-  </si>
-  <si>
-    <t>Globulin [Mass/volume] in Serum or Plasma by calculation</t>
-  </si>
-  <si>
-    <t>14390-9</t>
-  </si>
-  <si>
-    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
-  </si>
-  <si>
-    <t>14409-7</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
-  </si>
-  <si>
-    <t>1742-6</t>
-  </si>
-  <si>
-    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1744-2</t>
-  </si>
-  <si>
-    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
-  </si>
-  <si>
-    <t>1751-7</t>
-  </si>
-  <si>
-    <t>Albumin [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1759-0</t>
-  </si>
-  <si>
-    <t>Albumin/Globulin [Mass Ratio] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1783-0</t>
-  </si>
-  <si>
-    <t>Alkaline phosphatase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1798-8</t>
-  </si>
-  <si>
-    <t>Amylase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1920-8</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1968-7</t>
-  </si>
-  <si>
-    <t>Bilirubin.direct [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1975-2</t>
-  </si>
-  <si>
-    <t>Bilirubin.total [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2532-0</t>
-  </si>
-  <si>
-    <t>Lactate dehydrogenase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2885-2</t>
-  </si>
-  <si>
-    <t>Protein [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>3040-3</t>
-  </si>
-  <si>
-    <t>Lipase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>6768-6</t>
-  </si>
-  <si>
-    <t>88112-8</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
-  </si>
-  <si>
-    <t>46986-6</t>
-  </si>
-  <si>
-    <t>Cholesterol in VLDL [Mass/volume] in Serum or Plasma by calculation</t>
-  </si>
-  <si>
-    <t>9830-1</t>
-  </si>
-  <si>
-    <t>Cholesterol/Cholesterol in HDL [Mass Ratio] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2132-9</t>
-  </si>
-  <si>
-    <t>Cobalamin (Vitamin B12) [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2284-8</t>
-  </si>
-  <si>
-    <t>Folate [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>3016-3</t>
-  </si>
-  <si>
-    <t>Thyrotropin [Units/volume] in Serum or Plasma by 3rd IS</t>
-  </si>
-  <si>
-    <t>3026-2</t>
-  </si>
-  <si>
-    <t>Thyroxine (T4) total [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>3051-0</t>
-  </si>
-  <si>
-    <t>Triiodothyronine (T3) free [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>3053-6</t>
-  </si>
-  <si>
-    <t>Triiodothyronine (T3) total [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>62292-8</t>
-  </si>
-  <si>
-    <t>25-hydroxyvitamin D3 [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>8099-4</t>
-  </si>
-  <si>
-    <t>Thyroid peroxidase Ab [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>13950-1</t>
-  </si>
-  <si>
-    <t>Hepatitis A virus IgM Ab [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>13952-7</t>
-  </si>
-  <si>
-    <t>Hepatitis B virus core Ab [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>17780-8</t>
-  </si>
-  <si>
-    <t>Helicobacter pylori Ag [Presence] in Stool</t>
-  </si>
-  <si>
-    <t>20507-0</t>
-  </si>
-  <si>
-    <t>Reagin Ab [Presence] in Serum by RPR</t>
-  </si>
-  <si>
-    <t>21440-3</t>
-  </si>
-  <si>
-    <t>Human papilloma virus 16+18+31+33+35+45+51+52+56 DNA [Presence] in Cervix by Probe</t>
-  </si>
-  <si>
-    <t>22322-2</t>
-  </si>
-  <si>
-    <t>Hepatitis B virus surface Ab [Units/volume] in Serum</t>
-  </si>
-  <si>
-    <t>24110-9</t>
-  </si>
-  <si>
-    <t>Treponema pallidum Ab [Presence] in Serum by Immunoassay</t>
-  </si>
-  <si>
-    <t>29771-3</t>
-  </si>
-  <si>
-    <t>Hemoglobin.occult [Mass/volume] in Stool by Immunochemical method</t>
-  </si>
-  <si>
-    <t>31147-2</t>
-  </si>
-  <si>
-    <t>Reagin Ab [Presence] in Serum by RPR -- titer</t>
-  </si>
-  <si>
-    <t>5176-3</t>
-  </si>
-  <si>
-    <t>Helicobacter pylori IgG Ab [Presence] in Serum</t>
-  </si>
-  <si>
-    <t>51913-2</t>
-  </si>
-  <si>
-    <t>Hepatitis A virus Ab [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5193-8</t>
-  </si>
-  <si>
-    <t>Hepatitis B virus surface Ab [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5334-8</t>
-  </si>
-  <si>
-    <t>Rubella virus IgG Ab [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5403-1</t>
-  </si>
-  <si>
-    <t>Varicella zoster virus IgG Ab [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>56888-1</t>
-  </si>
-  <si>
-    <t>HIV 1 and 2 Ag and Ab panel [Presence] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>7962-4</t>
-  </si>
-  <si>
-    <t>Measles virus IgG Ab [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>11218-5</t>
-  </si>
-  <si>
-    <t>Microalbumin [Mass/volume] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>11277-1</t>
-  </si>
-  <si>
-    <t>Epithelial cells.squamous [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>12453-7</t>
-  </si>
-  <si>
-    <t>Amorphous phosphate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>12454-5</t>
-  </si>
-  <si>
-    <t>Amorphous urate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>13658-0</t>
-  </si>
-  <si>
-    <t>Urobilinogen [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>13945-1</t>
-  </si>
-  <si>
-    <t>Erythrocytes [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>20456-0</t>
-  </si>
-  <si>
-    <t>Fungi yeast-like [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>20621-9</t>
-  </si>
-  <si>
-    <t>Albumin/Creatinine [Ratio] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>20627-6</t>
-  </si>
-  <si>
-    <t>Color of Urine</t>
-  </si>
-  <si>
-    <t>25145-4</t>
-  </si>
-  <si>
-    <t>Bacteria [Presence] in Urine sediment by Light microscopy</t>
-  </si>
-  <si>
-    <t>30004-6</t>
-  </si>
-  <si>
-    <t>Creatinine [Mass/volume] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>32356-8</t>
-  </si>
-  <si>
-    <t>Yeast [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>33218-9</t>
-  </si>
-  <si>
-    <t>Bacteria [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33219-7</t>
-  </si>
-  <si>
-    <t>Epithelial cells.squamous [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33223-9</t>
-  </si>
-  <si>
-    <t>Hyaline casts [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33342-7</t>
-  </si>
-  <si>
-    <t>Epithelial cells [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>43755-8</t>
-  </si>
-  <si>
-    <t>Casts [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>46419-8</t>
-  </si>
-  <si>
-    <t>Erythrocytes [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>46702-7</t>
-  </si>
-  <si>
-    <t>Leukocytes [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>50235-1</t>
-  </si>
-  <si>
-    <t>Mucus [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>50551-1</t>
-  </si>
-  <si>
-    <t>Bilirubin [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>50555-2</t>
-  </si>
-  <si>
-    <t>Glucose [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>50558-6</t>
-  </si>
-  <si>
-    <t>Nitrite [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>50560-2</t>
-  </si>
-  <si>
-    <t>pH of Urine by Test strip</t>
-  </si>
-  <si>
-    <t>50562-8</t>
-  </si>
-  <si>
-    <t>Specific gravity of Urine by Refractometer</t>
-  </si>
-  <si>
-    <t>53324-0</t>
-  </si>
-  <si>
-    <t>Spermatozoa [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>53975-9</t>
-  </si>
-  <si>
-    <t>Drug crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5766-1</t>
-  </si>
-  <si>
-    <t>Ammonium acid urate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5770-3</t>
-  </si>
-  <si>
-    <t>5771-1</t>
-  </si>
-  <si>
-    <t>Bilirubin crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5773-7</t>
-  </si>
-  <si>
-    <t>Calcium carbonate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>57734-6</t>
-  </si>
-  <si>
-    <t>Ketones [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>5774-5</t>
-  </si>
-  <si>
-    <t>Calcium oxalate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5775-2</t>
-  </si>
-  <si>
-    <t>Calcium phosphate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>57751-0</t>
-  </si>
-  <si>
-    <t>Hemoglobin [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>5777-8</t>
-  </si>
-  <si>
-    <t>Cholesterol crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5784-4</t>
-  </si>
-  <si>
-    <t>Cystine crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5787-7</t>
-  </si>
-  <si>
-    <t>Epithelial cells [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>5788-5</t>
-  </si>
-  <si>
-    <t>Oval fat bodies [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>5792-7</t>
-  </si>
-  <si>
-    <t>5794-3</t>
-  </si>
-  <si>
-    <t>5796-8</t>
-  </si>
-  <si>
-    <t>Hyaline casts [#/area] in Urine sediment by Microscopy low power field</t>
-  </si>
-  <si>
-    <t>5797-6</t>
-  </si>
-  <si>
-    <t>5799-2</t>
-  </si>
-  <si>
-    <t>Leukocyte esterase [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>5802-4</t>
-  </si>
-  <si>
-    <t>5803-2</t>
-  </si>
-  <si>
-    <t>5813-1</t>
-  </si>
-  <si>
-    <t>Trichomonas vaginalis [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5814-9</t>
-  </si>
-  <si>
-    <t>Calcium magnesium ammonium phosphate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5817-2</t>
-  </si>
-  <si>
-    <t>Uric acid crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5821-4</t>
-  </si>
-  <si>
-    <t>Leukocytes [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>60026-2</t>
-  </si>
-  <si>
-    <t>62487-4</t>
-  </si>
-  <si>
-    <t>13705-9</t>
-  </si>
-  <si>
-    <t>Albumin/Creatinine [Mass Ratio] in Urine</t>
-  </si>
-  <si>
-    <t>14957-5</t>
-  </si>
-  <si>
-    <t>Microalbumin [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>1988-5</t>
-  </si>
-  <si>
-    <t>C reactive protein [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2161-8</t>
-  </si>
-  <si>
-    <t>Creatinine [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>4588-0</t>
-  </si>
-  <si>
-    <t>Hemoglobin H/Hemoglobin.total in Blood</t>
-  </si>
-  <si>
-    <t>10701-1</t>
-  </si>
-  <si>
-    <t>Ova and parasites [Presence] in Stool by Concentration method</t>
-  </si>
-  <si>
-    <t>10704-5</t>
-  </si>
-  <si>
-    <t>Ova and parasites [Presence] in Stool by Microscopy</t>
-  </si>
-  <si>
-    <t>13655-6</t>
-  </si>
-  <si>
-    <t>Leukocytes [Presence] in Stool by Microscopy</t>
-  </si>
-  <si>
-    <t>2335-8</t>
-  </si>
-  <si>
-    <t>Hemoglobin [Presence] in Stool</t>
-  </si>
-  <si>
-    <t>33668-5</t>
-  </si>
-  <si>
-    <t>Erythrocytes [Presence] in Stool by Microscopy</t>
-  </si>
-  <si>
-    <t>42524-9</t>
-  </si>
-  <si>
-    <t>Mucus [Presence] in Stool by Microscopy</t>
-  </si>
-  <si>
-    <t>9397-1</t>
-  </si>
-  <si>
-    <t>Color of Stool</t>
-  </si>
-  <si>
-    <t>19868-9</t>
-  </si>
-  <si>
-    <t>Forced vital capacity [Volume] Respiratory system by Spirometry</t>
   </si>
   <si>
     <t>98497-1</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="571">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,96 +231,6 @@
     <t>Hearing threshold Ear - right --8000 Hz</t>
   </si>
   <si>
-    <t>21104-5</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Audiometry study（panel 變異）</t>
-  </si>
-  <si>
-    <t>21106-0</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Left ear 500 Hz</t>
-  </si>
-  <si>
-    <t>21111-0</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Left ear 1000 Hz</t>
-  </si>
-  <si>
-    <t>21113-6</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Left ear 2000 Hz</t>
-  </si>
-  <si>
-    <t>21115-1</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Left ear 3000 Hz</t>
-  </si>
-  <si>
-    <t>21116-9</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Left ear 4000 Hz</t>
-  </si>
-  <si>
-    <t>21117-7</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Left ear 6000 Hz</t>
-  </si>
-  <si>
-    <t>21118-5</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Left ear 8000 Hz</t>
-  </si>
-  <si>
-    <t>21120-1</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Right ear 500 Hz</t>
-  </si>
-  <si>
-    <t>21123-5</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Right ear 1000 Hz</t>
-  </si>
-  <si>
-    <t>21125-0</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Right ear 2000 Hz</t>
-  </si>
-  <si>
-    <t>21127-6</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Right ear 3000 Hz</t>
-  </si>
-  <si>
-    <t>21128-4</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Right ear 4000 Hz</t>
-  </si>
-  <si>
-    <t>21129-2</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Right ear 6000 Hz</t>
-  </si>
-  <si>
-    <t>21130-0</t>
-  </si>
-  <si>
-    <t>Pure tone audiometry - Right ear 8000 Hz</t>
-  </si>
-  <si>
     <t>789-8</t>
   </si>
   <si>
@@ -360,7 +270,7 @@
     <t>736-9</t>
   </si>
   <si>
-    <t>Lymphocytes [Fraction] of WBC</t>
+    <t>Lymphocytes/Leukocytes in Blood by Automated count</t>
   </si>
   <si>
     <t>11580-8</t>
@@ -426,7 +336,7 @@
     <t>11215-1</t>
   </si>
   <si>
-    <t>Aminolevulinic acid [Mass/volume] in Urine</t>
+    <t>Delta aminolevulinate [Mass/volume] in Urine</t>
   </si>
   <si>
     <t>36643-5</t>
@@ -1171,12 +1081,6 @@
   </si>
   <si>
     <t>Homeostasis model assessment</t>
-  </si>
-  <si>
-    <t>49154-8</t>
-  </si>
-  <si>
-    <t>Uric acid [Mass/volume] in Blood</t>
   </si>
   <si>
     <t>59261-8</t>
@@ -2093,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B279"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2817,124 +2721,124 @@
         <v>206</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>219</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>229</v>
+        <v>201</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>235</v>
@@ -2942,90 +2846,90 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>240</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>242</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>246</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>248</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>250</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>256</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>231</v>
       </c>
     </row>
     <row r="117">
@@ -3137,127 +3041,127 @@
         <v>284</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>285</v>
+        <v>75</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B131" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B132" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B133" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>291</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B134" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B135" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B136" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B137" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>299</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B138" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B139" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>303</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B140" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B141" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B142" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>309</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B143" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B144" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B145" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>105</v>
       </c>
     </row>
     <row r="146">
@@ -3321,127 +3225,127 @@
         <v>329</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>330</v>
+        <v>302</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B154" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B155" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B156" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>336</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B157" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B158" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B159" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B160" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B161" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B162" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>348</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B163" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B164" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B165" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>354</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>356</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B167" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B168" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="169">
@@ -3569,135 +3473,135 @@
         <v>390</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B185" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B186" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B187" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>397</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B188" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B189" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>401</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B190" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>403</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B191" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B192" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B193" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>411</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B195" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>413</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B196" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B197" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B198" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B199" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>421</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B200" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="201">
@@ -4017,447 +3921,319 @@
         <v>501</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>502</v>
+        <v>486</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B241" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>504</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B242" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>506</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B243" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>508</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B244" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>510</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B245" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B246" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="B246" t="s" s="2">
-        <v>514</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B247" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>516</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B248" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>518</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B249" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B250" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>522</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>524</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>526</v>
+        <v>513</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>530</v>
+        <v>507</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>518</v>
+        <v>490</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>535</v>
+        <v>492</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>545</v>
+        <v>528</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>547</v>
+        <v>454</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>520</v>
+        <v>548</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>539</v>
+        <v>554</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>522</v>
+        <v>558</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>524</v>
+        <v>560</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>571</v>
+        <v>22</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>560</v>
+        <v>22</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="B280" t="s" s="2">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="B281" t="s" s="2">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B282" t="s" s="2">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="B283" t="s" s="2">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B284" t="s" s="2">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="B285" t="s" s="2">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="B286" t="s" s="2">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B287" t="s" s="2">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="B288" t="s" s="2">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="B289" t="s" s="2">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="B290" t="s" s="2">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="B291" t="s" s="2">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="B292" t="s" s="2">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="B293" t="s" s="2">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B294" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B295" t="s" s="2">
-        <v>602</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="573">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -309,6 +309,12 @@
     <t>FEV1/FVC</t>
   </si>
   <si>
+    <t>77307-7</t>
+  </si>
+  <si>
+    <t>Lead [Mass/volume] in Venous blood</t>
+  </si>
+  <si>
     <t>5671-3</t>
   </si>
   <si>
@@ -585,34 +591,34 @@
     <t>Salmonella and Shigella [Presence] in Stool by Culture</t>
   </si>
   <si>
-    <t>19266-6</t>
-  </si>
-  <si>
-    <t>Amphetamines [Presence] in Urine by Screening test</t>
-  </si>
-  <si>
-    <t>19299-7</t>
-  </si>
-  <si>
-    <t>Opiates [Presence] in Urine by Screening test</t>
-  </si>
-  <si>
-    <t>19283-1</t>
-  </si>
-  <si>
-    <t>Benzodiazepines [Presence] in Urine by Screening test</t>
-  </si>
-  <si>
-    <t>19501-6</t>
-  </si>
-  <si>
-    <t>Ketamine [Presence] in Urine by Screening test</t>
-  </si>
-  <si>
-    <t>19571-9</t>
-  </si>
-  <si>
-    <t>MDMA [Presence] in Urine by Screening test</t>
+    <t>3349-8</t>
+  </si>
+  <si>
+    <t>Amphetamines [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>3879-4</t>
+  </si>
+  <si>
+    <t>Opiates [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>3390-2</t>
+  </si>
+  <si>
+    <t>Benzodiazepines [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>12327-3</t>
+  </si>
+  <si>
+    <t>Ketamine [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>14267-9</t>
+  </si>
+  <si>
+    <t>Methylenedioxymethamphetamine [Presence] in Urine</t>
   </si>
   <si>
     <t>19177-5</t>
@@ -1299,7 +1305,7 @@
     <t>29771-3</t>
   </si>
   <si>
-    <t>Hemoglobin.occult [Mass/volume] in Stool by Immunochemical method</t>
+    <t>Hemoglobin [Presence] in Stool from gastrointestinal lower by Immunoassay</t>
   </si>
   <si>
     <t>31147-2</t>
@@ -1997,7 +2003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B279"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2721,15 +2727,15 @@
         <v>206</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="92">
@@ -2809,15 +2815,15 @@
         <v>227</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>201</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>229</v>
+        <v>203</v>
       </c>
     </row>
     <row r="103">
@@ -3041,15 +3047,15 @@
         <v>284</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>75</v>
+        <v>285</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>286</v>
+        <v>75</v>
       </c>
     </row>
     <row r="132">
@@ -3225,15 +3231,15 @@
         <v>329</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>302</v>
+        <v>330</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>331</v>
+        <v>304</v>
       </c>
     </row>
     <row r="155">
@@ -3473,15 +3479,15 @@
         <v>390</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>375</v>
+        <v>391</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>392</v>
+        <v>377</v>
       </c>
     </row>
     <row r="186">
@@ -3921,15 +3927,15 @@
         <v>501</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>486</v>
+        <v>502</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>503</v>
+        <v>488</v>
       </c>
     </row>
     <row r="242">
@@ -4009,23 +4015,23 @@
         <v>522</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>488</v>
+        <v>523</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>513</v>
+        <v>490</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="254">
@@ -4033,15 +4039,15 @@
         <v>526</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>507</v>
+        <v>527</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>528</v>
+        <v>509</v>
       </c>
     </row>
     <row r="256">
@@ -4049,12 +4055,12 @@
         <v>529</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>490</v>
+        <v>530</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>492</v>
@@ -4062,10 +4068,10 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>532</v>
+        <v>494</v>
       </c>
     </row>
     <row r="259">
@@ -4097,23 +4103,23 @@
         <v>539</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>528</v>
+        <v>540</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>454</v>
+        <v>530</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>542</v>
+        <v>456</v>
       </c>
     </row>
     <row r="265">
@@ -4222,18 +4228,26 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>22</v>
+        <v>569</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>22</v>
+        <v>570</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>569</v>
+        <v>22</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>570</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B280" t="s" s="2">
+        <v>572</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="590">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -138,7 +138,7 @@
     <t>5810-7</t>
   </si>
   <si>
-    <t>Specific gravity of Urine</t>
+    <t>Specific gravity of Urine by Refractometry</t>
   </si>
   <si>
     <t>89015-2</t>
@@ -234,1006 +234,1033 @@
     <t>789-8</t>
   </si>
   <si>
-    <t>Erythrocytes [#/volume] in Blood</t>
+    <t>Erythrocytes [#/volume] in Blood by Automated count</t>
   </si>
   <si>
     <t>6690-2</t>
   </si>
   <si>
-    <t>WBC [#/volume] in Blood</t>
+    <t>Leukocytes [#/volume] in Blood by Automated count</t>
   </si>
   <si>
     <t>777-3</t>
   </si>
   <si>
+    <t>Platelets [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>718-7</t>
+  </si>
+  <si>
+    <t>Hemoglobin [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>4544-3</t>
+  </si>
+  <si>
+    <t>Hematocrit [Volume Fraction] of Blood by Automated count</t>
+  </si>
+  <si>
+    <t>770-8</t>
+  </si>
+  <si>
+    <t>Neutrophils/Leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>736-9</t>
+  </si>
+  <si>
+    <t>Lymphocytes/Leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>11580-8</t>
+  </si>
+  <si>
+    <t>Thyrotropin [Units/volume] in Serum or Plasma by Detection limit &lt;= 0.005 mIU/L</t>
+  </si>
+  <si>
+    <t>3024-7</t>
+  </si>
+  <si>
+    <t>Thyroxine (T4) free [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>24579-5</t>
+  </si>
+  <si>
+    <t>XR Bones.long Survey</t>
+  </si>
+  <si>
+    <t>19868-9</t>
+  </si>
+  <si>
+    <t>Forced vital capacity [Volume] Respiratory system by Spirometry</t>
+  </si>
+  <si>
+    <t>20150-9</t>
+  </si>
+  <si>
+    <t>FEV1</t>
+  </si>
+  <si>
+    <t>19926-5</t>
+  </si>
+  <si>
+    <t>FEV1/FVC</t>
+  </si>
+  <si>
+    <t>77307-7</t>
+  </si>
+  <si>
+    <t>Lead [Mass/volume] in Venous blood</t>
+  </si>
+  <si>
+    <t>5671-3</t>
+  </si>
+  <si>
+    <t>Lead [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5676-2</t>
+  </si>
+  <si>
+    <t>Lead [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>23749-5</t>
+  </si>
+  <si>
+    <t>Lead [Mass/volume] in Specimen</t>
+  </si>
+  <si>
+    <t>11212-8</t>
+  </si>
+  <si>
+    <t>Coproporphyrin [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>11215-1</t>
+  </si>
+  <si>
+    <t>Delta aminolevulinate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>36643-5</t>
+  </si>
+  <si>
+    <t>XR Chest 2 Views</t>
+  </si>
+  <si>
+    <t>24648-8</t>
+  </si>
+  <si>
+    <t>XR Chest PA upright</t>
+  </si>
+  <si>
+    <t>2324-2</t>
+  </si>
+  <si>
+    <t>Gamma glutamyl transferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>6709-0</t>
+  </si>
+  <si>
+    <t>Hippurate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>2725-0</t>
+  </si>
+  <si>
+    <t>Para methylhippurate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>13000-5</t>
+  </si>
+  <si>
+    <t>Mandelate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>3041-1</t>
+  </si>
+  <si>
+    <t>Trichloroacetate [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>31170-4</t>
+  </si>
+  <si>
+    <t>2,5-Hexanedione [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>2758-1</t>
+  </si>
+  <si>
+    <t>Phenol [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>12543-5</t>
+  </si>
+  <si>
+    <t>Methyl formamide [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>12533-6</t>
+  </si>
+  <si>
+    <t>Thiazolidine-2-Thione-4-Carboxylic acid [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5586-3</t>
+  </si>
+  <si>
+    <t>Arsenic [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5609-3</t>
+  </si>
+  <si>
+    <t>Cadmium [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5611-9</t>
+  </si>
+  <si>
+    <t>Cadmium [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>13471-8</t>
+  </si>
+  <si>
+    <t>Cadmium/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
+    <t>5622-6</t>
+  </si>
+  <si>
+    <t>Chromium [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5623-4</t>
+  </si>
+  <si>
+    <t>Chromium [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>13464-3</t>
+  </si>
+  <si>
+    <t>Chromium/Creatinine [Mass Ratio] in Urine</t>
+  </si>
+  <si>
+    <t>14099-6</t>
+  </si>
+  <si>
+    <t>Nickel [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5685-3</t>
+  </si>
+  <si>
+    <t>Mercury [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5689-5</t>
+  </si>
+  <si>
+    <t>Mercury [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>72665-3</t>
+  </si>
+  <si>
+    <t>trans,trans-Muconic acid [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>10913-2</t>
+  </si>
+  <si>
+    <t>4,4'-Methylene bis(2-Chloroaniline) [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5653-1</t>
+  </si>
+  <si>
+    <t>Formaldehyde [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>10909-0</t>
+  </si>
+  <si>
+    <t>Benzidine [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5681-2</t>
+  </si>
+  <si>
+    <t>Manganese [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5683-8</t>
+  </si>
+  <si>
+    <t>Manganese [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>42221-2</t>
+  </si>
+  <si>
+    <t>Manganese [Moles/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5684-6</t>
+  </si>
+  <si>
+    <t>Manganese [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>34304-6</t>
+  </si>
+  <si>
+    <t>Fluoride [Moles/volume] in Urine</t>
+  </si>
+  <si>
+    <t>5650-7</t>
+  </si>
+  <si>
+    <t>Fluoride [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>2777-1</t>
+  </si>
+  <si>
+    <t>Phosphate [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>24829-4</t>
+  </si>
+  <si>
+    <t>XR Mandible Views</t>
+  </si>
+  <si>
+    <t>9827-7</t>
+  </si>
+  <si>
+    <t>Paraquat [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>60090-8</t>
+  </si>
+  <si>
+    <t>Indium [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5665-5</t>
+  </si>
+  <si>
+    <t>Indium [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>5627-5</t>
+  </si>
+  <si>
+    <t>Cobalt [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>5625-9</t>
+  </si>
+  <si>
+    <t>Cobalt [Mass/volume] in Blood</t>
+  </si>
+  <si>
+    <t>1984-4</t>
+  </si>
+  <si>
+    <t>Bromide [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1985-1</t>
+  </si>
+  <si>
+    <t>Bromide [Mass/volume] in Urine</t>
+  </si>
+  <si>
+    <t>1709-5</t>
+  </si>
+  <si>
+    <t>Acetylcholinesterase [Enzymatic activity/volume] in Red Blood Cells</t>
+  </si>
+  <si>
+    <t>2098-2</t>
+  </si>
+  <si>
+    <t>Cholinesterase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>43371-4</t>
+  </si>
+  <si>
+    <t>Salmonella and Shigella sp identified in Stool by Organism specific culture</t>
+  </si>
+  <si>
+    <t>3349-8</t>
+  </si>
+  <si>
+    <t>Amphetamines [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>3879-4</t>
+  </si>
+  <si>
+    <t>Opiates [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>3390-2</t>
+  </si>
+  <si>
+    <t>Benzodiazepines [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>12327-3</t>
+  </si>
+  <si>
+    <t>Ketamine [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>14267-9</t>
+  </si>
+  <si>
+    <t>Methylenedioxymethamphetamine [Presence] in Urine</t>
+  </si>
+  <si>
+    <t>19177-5</t>
+  </si>
+  <si>
+    <t>Alpha-1-Fetoprotein [Moles/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>53962-7</t>
+  </si>
+  <si>
+    <t>Alpha-1-fetoprotein.tumor marker [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2039-6</t>
+  </si>
+  <si>
+    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2857-1</t>
+  </si>
+  <si>
+    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>10886-0</t>
+  </si>
+  <si>
+    <t>Prostate Specific Ag Free [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>97149-9</t>
+  </si>
+  <si>
+    <t>proPSA isoform 2 [Mass/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>97150-7</t>
+  </si>
+  <si>
+    <t>Prostate health index in Serum or Plasma by calculation</t>
+  </si>
+  <si>
+    <t>10334-1</t>
+  </si>
+  <si>
+    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>83082-8</t>
+  </si>
+  <si>
+    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>83085-1</t>
+  </si>
+  <si>
+    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>24108-3</t>
+  </si>
+  <si>
+    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>83084-4</t>
+  </si>
+  <si>
+    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>83083-6</t>
+  </si>
+  <si>
+    <t>Cancer Ag 15-3 [Units/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>83112-3</t>
+  </si>
+  <si>
+    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
+  </si>
+  <si>
+    <t>1834-1</t>
+  </si>
+  <si>
+    <t>Alpha-1-fetoprotein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>9679-2</t>
+  </si>
+  <si>
+    <t>Squamous cell carcinoma Ag [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>19113-0</t>
+  </si>
+  <si>
+    <t>IgE [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>9633-9</t>
+  </si>
+  <si>
+    <t>Epstein Barr virus capsid IgA Ab [Titer] in Serum by Immunofluorescence</t>
+  </si>
+  <si>
+    <t>10835-7</t>
+  </si>
+  <si>
+    <t>Lipoprotein A [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1869-7</t>
+  </si>
+  <si>
+    <t>Apolipoprotein A-I [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1884-6</t>
+  </si>
+  <si>
+    <t>Apolipoprotein B [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>33762-6</t>
+  </si>
+  <si>
+    <t>Natriuretic peptide.B prohormone N-Terminal [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>42254-3</t>
+  </si>
+  <si>
+    <t>Nuclear Ab [Presence] in Serum by Immunofluorescence</t>
+  </si>
+  <si>
+    <t>11572-5</t>
+  </si>
+  <si>
+    <t>Rheumatoid factor [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>25390-6</t>
+  </si>
+  <si>
+    <t>Cytokeratin 19 [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>24606-6</t>
+  </si>
+  <si>
+    <t>MG Breast Screening</t>
+  </si>
+  <si>
+    <t>103892-6</t>
+  </si>
+  <si>
+    <t>DBT Brst Screening</t>
+  </si>
+  <si>
+    <t>24590-2</t>
+  </si>
+  <si>
+    <t>MR Brain</t>
+  </si>
+  <si>
+    <t>79086-5</t>
+  </si>
+  <si>
+    <t>CT Chest Screening WO contr</t>
+  </si>
+  <si>
+    <t>87279-6</t>
+  </si>
+  <si>
+    <t>CT Chest Screening</t>
+  </si>
+  <si>
+    <t>81555-5</t>
+  </si>
+  <si>
+    <t>PT+CT Whole body Tum loc W 18F-FDG IV</t>
+  </si>
+  <si>
+    <t>79073-3</t>
+  </si>
+  <si>
+    <t>CTA Hrt+CA W contr IV</t>
+  </si>
+  <si>
+    <t>28014-9</t>
+  </si>
+  <si>
+    <t>EGD Study</t>
+  </si>
+  <si>
+    <t>28023-0</t>
+  </si>
+  <si>
+    <t>Colonoscopy Study</t>
+  </si>
+  <si>
+    <t>24558-9</t>
+  </si>
+  <si>
+    <t>US Abdomen</t>
+  </si>
+  <si>
+    <t>24616-5</t>
+  </si>
+  <si>
+    <t>US Carotid aa</t>
+  </si>
+  <si>
+    <t>25010-0</t>
+  </si>
+  <si>
+    <t>US Thyroid</t>
+  </si>
+  <si>
+    <t>38268-9</t>
+  </si>
+  <si>
+    <t>DXA Skeletal Sys Views for BMD</t>
+  </si>
+  <si>
+    <t>13046-8</t>
+  </si>
+  <si>
+    <t>Variant lymphocytes/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>13047-6</t>
+  </si>
+  <si>
+    <t>Plasma cells/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>19048-8</t>
+  </si>
+  <si>
+    <t>Nucleated erythrocytes/Leukocytes [Ratio] in Blood</t>
+  </si>
+  <si>
+    <t>26446-5</t>
+  </si>
+  <si>
+    <t>Blasts/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26450-7</t>
+  </si>
+  <si>
+    <t>Eosinophils/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26464-8</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/volume] in Blood</t>
+  </si>
+  <si>
+    <t>26478-8</t>
+  </si>
+  <si>
+    <t>Lymphocytes/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26485-3</t>
+  </si>
+  <si>
+    <t>Monocytes/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26498-6</t>
+  </si>
+  <si>
+    <t>Myelocytes/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26505-8</t>
+  </si>
+  <si>
+    <t>Segmented neutrophils/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26508-2</t>
+  </si>
+  <si>
+    <t>Band form neutrophils/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26511-6</t>
+  </si>
+  <si>
+    <t>Neutrophils/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>26515-7</t>
+  </si>
+  <si>
     <t>Platelets [#/volume] in Blood</t>
   </si>
   <si>
-    <t>718-7</t>
-  </si>
-  <si>
-    <t>Hemoglobin [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>4544-3</t>
-  </si>
-  <si>
-    <t>Hematocrit [Volume Fraction] of Blood</t>
-  </si>
-  <si>
-    <t>770-8</t>
-  </si>
-  <si>
-    <t>Neutrophils [Fraction] of WBC</t>
-  </si>
-  <si>
-    <t>736-9</t>
-  </si>
-  <si>
-    <t>Lymphocytes/Leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>11580-8</t>
+    <t>26524-9</t>
+  </si>
+  <si>
+    <t>Promyelocytes/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>28539-5</t>
+  </si>
+  <si>
+    <t>MCH [Entitic mass]</t>
+  </si>
+  <si>
+    <t>28541-1</t>
+  </si>
+  <si>
+    <t>Metamyelocytes/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30180-4</t>
+  </si>
+  <si>
+    <t>Basophils/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30413-9</t>
+  </si>
+  <si>
+    <t>Abnormal lymphocytes/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30428-7</t>
+  </si>
+  <si>
+    <t>MCV [Entitic mean volume] in Red Blood Cells</t>
+  </si>
+  <si>
+    <t>30441-0</t>
+  </si>
+  <si>
+    <t>Monocytes Abnormal/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>30466-7</t>
+  </si>
+  <si>
+    <t>Promonocytes/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>34921-7</t>
+  </si>
+  <si>
+    <t>Lymphocytes Plasmacytoid/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>5905-5</t>
+  </si>
+  <si>
+    <t>Monocytes/Leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>19252-6</t>
+  </si>
+  <si>
+    <t>Megakaryocytes/Leukocytes in Blood</t>
+  </si>
+  <si>
+    <t>706-2</t>
+  </si>
+  <si>
+    <t>Basophils/Leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>713-8</t>
+  </si>
+  <si>
+    <t>Eosinophils/Leukocytes in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>731-0</t>
+  </si>
+  <si>
+    <t>Lymphocytes [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>751-8</t>
+  </si>
+  <si>
+    <t>Neutrophils [#/volume] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>785-6</t>
+  </si>
+  <si>
+    <t>MCH [Entitic mass] by Automated count</t>
+  </si>
+  <si>
+    <t>786-4</t>
+  </si>
+  <si>
+    <t>MCHC [Entitic Mass/volume] in Red Blood Cells by Automated count</t>
+  </si>
+  <si>
+    <t>787-2</t>
+  </si>
+  <si>
+    <t>MCV [Entitic mean volume] in Red Blood Cells by Automated count</t>
+  </si>
+  <si>
+    <t>788-0</t>
+  </si>
+  <si>
+    <t>Erythrocyte [DistWidth] in Blood by Automated count</t>
+  </si>
+  <si>
+    <t>804-5</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/volume] in Blood by Manual count</t>
+  </si>
+  <si>
+    <t>17861-6</t>
+  </si>
+  <si>
+    <t>Calcium [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>20448-7</t>
+  </si>
+  <si>
+    <t>Insulin [Units/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2428-1</t>
+  </si>
+  <si>
+    <t>Homocysteine [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>13965-9</t>
+  </si>
+  <si>
+    <t>Homocysteine [Moles/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>30522-7</t>
+  </si>
+  <si>
+    <t>C reactive protein [Mass/volume] in Serum or Plasma by High sensitivity method</t>
+  </si>
+  <si>
+    <t>3084-1</t>
+  </si>
+  <si>
+    <t>Urate [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>33863-2</t>
+  </si>
+  <si>
+    <t>Cystatin C [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>33914-3</t>
+  </si>
+  <si>
+    <t>Glomerular filtration rate [Volume Rate/Area] in Serum or Plasma by Creatinine-based formula (MDRD)/1.73 sq M</t>
+  </si>
+  <si>
+    <t>4548-4</t>
+  </si>
+  <si>
+    <t>Hemoglobin A1c/Hemoglobin.total in Blood</t>
+  </si>
+  <si>
+    <t>47214-2</t>
+  </si>
+  <si>
+    <t>Homeostasis model assessment</t>
+  </si>
+  <si>
+    <t>59261-8</t>
+  </si>
+  <si>
+    <t>Hemoglobin A1c/Hemoglobin.total standardized per IFCC-RMP for CDT in Blood</t>
+  </si>
+  <si>
+    <t>98979-8</t>
+  </si>
+  <si>
+    <t>Glomerular filtration rate [Volume Rate/Area] in Serum, Plasma or Blood by Creatinine-based formula (CKD-EPI 2021)/1.73 sq M</t>
+  </si>
+  <si>
+    <t>10834-0</t>
+  </si>
+  <si>
+    <t>Globulin [Mass/volume] in Serum by calculation</t>
+  </si>
+  <si>
+    <t>1743-4</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by With P-5'-P</t>
+  </si>
+  <si>
+    <t>30239-8</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by With P-5'-P</t>
+  </si>
+  <si>
+    <t>1742-6</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1744-2</t>
+  </si>
+  <si>
+    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+  </si>
+  <si>
+    <t>1751-7</t>
+  </si>
+  <si>
+    <t>Albumin [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1759-0</t>
+  </si>
+  <si>
+    <t>Albumin/Globulin [Mass Ratio] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1798-8</t>
+  </si>
+  <si>
+    <t>Amylase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1920-8</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1968-7</t>
+  </si>
+  <si>
+    <t>Bilirubin.direct [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>1975-2</t>
+  </si>
+  <si>
+    <t>Bilirubin.total [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2532-0</t>
+  </si>
+  <si>
+    <t>Lactate dehydrogenase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2885-2</t>
+  </si>
+  <si>
+    <t>Protein [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3040-3</t>
+  </si>
+  <si>
+    <t>Lipase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>6768-6</t>
+  </si>
+  <si>
+    <t>Alkaline phosphatase [Enzymatic activity/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>88112-8</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
+  </si>
+  <si>
+    <t>13458-5</t>
+  </si>
+  <si>
+    <t>Cholesterol in VLDL [Mass/volume] in Serum or Plasma by calculation</t>
+  </si>
+  <si>
+    <t>9830-1</t>
+  </si>
+  <si>
+    <t>Cholesterol.total/Cholesterol in HDL [Mass Ratio] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2132-9</t>
+  </si>
+  <si>
+    <t>Cobalamin (Vitamin B12) [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>2284-8</t>
+  </si>
+  <si>
+    <t>Folate [Mass/volume] in Serum or Plasma</t>
+  </si>
+  <si>
+    <t>3016-3</t>
   </si>
   <si>
     <t>Thyrotropin [Units/volume] in Serum or Plasma</t>
   </si>
   <si>
-    <t>3024-7</t>
-  </si>
-  <si>
-    <t>Thyroxine (T4) free [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>24579-5</t>
-  </si>
-  <si>
-    <t>XR Bones.long Survey</t>
-  </si>
-  <si>
-    <t>19868-9</t>
-  </si>
-  <si>
-    <t>Forced vital capacity [Volume] Respiratory system by Spirometry</t>
-  </si>
-  <si>
-    <t>20150-9</t>
-  </si>
-  <si>
-    <t>FEV1</t>
-  </si>
-  <si>
-    <t>19926-5</t>
-  </si>
-  <si>
-    <t>FEV1/FVC</t>
-  </si>
-  <si>
-    <t>77307-7</t>
-  </si>
-  <si>
-    <t>Lead [Mass/volume] in Venous blood</t>
-  </si>
-  <si>
-    <t>5671-3</t>
-  </si>
-  <si>
-    <t>Lead [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5676-2</t>
-  </si>
-  <si>
-    <t>Lead [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>23749-5</t>
-  </si>
-  <si>
-    <t>Lead [Mass/volume] in Specimen</t>
-  </si>
-  <si>
-    <t>11212-8</t>
-  </si>
-  <si>
-    <t>Coproporphyrin [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>11215-1</t>
-  </si>
-  <si>
-    <t>Delta aminolevulinate [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>36643-5</t>
-  </si>
-  <si>
-    <t>XR Chest 2 Views</t>
-  </si>
-  <si>
-    <t>24648-8</t>
-  </si>
-  <si>
-    <t>XR Chest PA upright</t>
-  </si>
-  <si>
-    <t>2324-2</t>
-  </si>
-  <si>
-    <t>Gamma glutamyltransferase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>6709-0</t>
-  </si>
-  <si>
-    <t>Hippurate [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>2725-0</t>
-  </si>
-  <si>
-    <t>p-Methylhippurate [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>13000-5</t>
-  </si>
-  <si>
-    <t>Mandelate [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>3041-1</t>
-  </si>
-  <si>
-    <t>Trichloroacetate [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>31170-4</t>
-  </si>
-  <si>
-    <t>2,5-Hexanedione [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>2758-1</t>
-  </si>
-  <si>
-    <t>Phenol [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>12543-5</t>
-  </si>
-  <si>
-    <t>Methylformamide [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>12533-6</t>
-  </si>
-  <si>
-    <t>TTCA [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5586-3</t>
-  </si>
-  <si>
-    <t>Arsenic [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5609-3</t>
-  </si>
-  <si>
-    <t>Cadmium [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5611-9</t>
-  </si>
-  <si>
-    <t>Cadmium [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>13471-8</t>
-  </si>
-  <si>
-    <t>Cadmium/Creatinine [Mass Ratio] in Urine</t>
-  </si>
-  <si>
-    <t>5622-6</t>
-  </si>
-  <si>
-    <t>Chromium [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5623-4</t>
-  </si>
-  <si>
-    <t>Chromium [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>13464-3</t>
-  </si>
-  <si>
-    <t>Chromium/Creatinine [Mass Ratio] in Urine</t>
-  </si>
-  <si>
-    <t>14099-6</t>
-  </si>
-  <si>
-    <t>Nickel [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5685-3</t>
-  </si>
-  <si>
-    <t>Mercury [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5689-5</t>
-  </si>
-  <si>
-    <t>Mercury [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>72665-3</t>
-  </si>
-  <si>
-    <t>trans,trans-Muconic acid [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>10913-2</t>
-  </si>
-  <si>
-    <t>4,4'-Methylenebis(2-chloroaniline) [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5653-1</t>
-  </si>
-  <si>
-    <t>Formaldehyde [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>10909-0</t>
-  </si>
-  <si>
-    <t>Benzidine [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>5681-2</t>
-  </si>
-  <si>
-    <t>Manganese [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5683-8</t>
-  </si>
-  <si>
-    <t>Manganese [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>42221-2</t>
-  </si>
-  <si>
-    <t>Manganese [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>34304-6</t>
-  </si>
-  <si>
-    <t>Fluoride [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>2777-1</t>
-  </si>
-  <si>
-    <t>Phosphate [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>24829-4</t>
-  </si>
-  <si>
-    <t>XR Mandible Views</t>
-  </si>
-  <si>
-    <t>9827-7</t>
-  </si>
-  <si>
-    <t>Paraquat [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>60090-8</t>
-  </si>
-  <si>
-    <t>Indium [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5665-5</t>
-  </si>
-  <si>
-    <t>Indium [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>5627-5</t>
-  </si>
-  <si>
-    <t>Cobalt [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>5625-9</t>
-  </si>
-  <si>
-    <t>Cobalt [Mass/volume] in Blood</t>
-  </si>
-  <si>
-    <t>1984-4</t>
-  </si>
-  <si>
-    <t>Bromide [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1985-1</t>
-  </si>
-  <si>
-    <t>Bromide [Mass/volume] in Urine</t>
-  </si>
-  <si>
-    <t>1709-5</t>
-  </si>
-  <si>
-    <t>Acetylcholinesterase [Enzymatic activity/volume] in Red Blood Cells</t>
-  </si>
-  <si>
-    <t>2098-2</t>
-  </si>
-  <si>
-    <t>Cholinesterase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>43371-4</t>
-  </si>
-  <si>
-    <t>Salmonella and Shigella [Presence] in Stool by Culture</t>
-  </si>
-  <si>
-    <t>3349-8</t>
-  </si>
-  <si>
-    <t>Amphetamines [Presence] in Urine</t>
-  </si>
-  <si>
-    <t>3879-4</t>
-  </si>
-  <si>
-    <t>Opiates [Presence] in Urine</t>
-  </si>
-  <si>
-    <t>3390-2</t>
-  </si>
-  <si>
-    <t>Benzodiazepines [Presence] in Urine</t>
-  </si>
-  <si>
-    <t>12327-3</t>
-  </si>
-  <si>
-    <t>Ketamine [Presence] in Urine</t>
-  </si>
-  <si>
-    <t>14267-9</t>
-  </si>
-  <si>
-    <t>Methylenedioxymethamphetamine [Presence] in Urine</t>
-  </si>
-  <si>
-    <t>19177-5</t>
-  </si>
-  <si>
-    <t>Alpha-1-fetoprotein [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2039-6</t>
-  </si>
-  <si>
-    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2857-1</t>
-  </si>
-  <si>
-    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>19199-9</t>
-  </si>
-  <si>
-    <t>10886-0</t>
-  </si>
-  <si>
-    <t>Prostate specific Ag.free [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>97149-9</t>
-  </si>
-  <si>
-    <t>[-2]pro-prostate specific antigen [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>97150-7</t>
-  </si>
-  <si>
-    <t>Prostate Health Index in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>10334-1</t>
-  </si>
-  <si>
-    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>83082-8</t>
-  </si>
-  <si>
-    <t>Cancer Ag 125 [Units/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>83085-1</t>
-  </si>
-  <si>
-    <t>Carcinoembryonic Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>24108-3</t>
-  </si>
-  <si>
-    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>83084-4</t>
-  </si>
-  <si>
-    <t>Cancer Ag 19-9 [Units/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>83083-6</t>
-  </si>
-  <si>
-    <t>Cancer Ag 15-3 [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>83112-3</t>
-  </si>
-  <si>
-    <t>Prostate specific Ag [Mass/volume] in Serum or Plasma by Immunoassay</t>
-  </si>
-  <si>
-    <t>1834-1</t>
-  </si>
-  <si>
-    <t>9679-2</t>
-  </si>
-  <si>
-    <t>Squamous cell carcinoma Ag [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>19113-0</t>
-  </si>
-  <si>
-    <t>IgE [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>9633-9</t>
-  </si>
-  <si>
-    <t>Epstein Barr virus VCA IgA Ab [Presence] in Serum</t>
-  </si>
-  <si>
-    <t>10835-7</t>
-  </si>
-  <si>
-    <t>Lipoprotein A [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1869-7</t>
-  </si>
-  <si>
-    <t>Apolipoprotein A-I [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1884-6</t>
-  </si>
-  <si>
-    <t>Apolipoprotein B [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>33762-6</t>
-  </si>
-  <si>
-    <t>Natriuretic peptide.proB-type N-terminal [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>42254-3</t>
-  </si>
-  <si>
-    <t>Nuclear Ab [Presence] in Serum by Immunofluorescence</t>
-  </si>
-  <si>
-    <t>11572-5</t>
-  </si>
-  <si>
-    <t>Rheumatoid factor [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>25390-6</t>
-  </si>
-  <si>
-    <t>CYFRA 21-1 [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>24606-6</t>
-  </si>
-  <si>
-    <t>MG Breast Screening</t>
-  </si>
-  <si>
-    <t>103892-6</t>
-  </si>
-  <si>
-    <t>DBT Brst Screening</t>
-  </si>
-  <si>
-    <t>24590-2</t>
-  </si>
-  <si>
-    <t>MR Brain</t>
-  </si>
-  <si>
-    <t>79086-5</t>
-  </si>
-  <si>
-    <t>CT Chest Screening WO contr</t>
-  </si>
-  <si>
-    <t>87279-6</t>
-  </si>
-  <si>
-    <t>CT Chest Screening</t>
-  </si>
-  <si>
-    <t>81555-5</t>
-  </si>
-  <si>
-    <t>PT+CT Whole body Tum loc W 18F-FDG IV</t>
-  </si>
-  <si>
-    <t>79073-3</t>
-  </si>
-  <si>
-    <t>CTA Hrt+CA W contr IV</t>
-  </si>
-  <si>
-    <t>28014-9</t>
-  </si>
-  <si>
-    <t>EGD Study</t>
-  </si>
-  <si>
-    <t>28023-0</t>
-  </si>
-  <si>
-    <t>Colonoscopy Study</t>
-  </si>
-  <si>
-    <t>24558-9</t>
-  </si>
-  <si>
-    <t>Ultrasound of abdomen study</t>
-  </si>
-  <si>
-    <t>24616-5</t>
-  </si>
-  <si>
-    <t>US Carotid aa</t>
-  </si>
-  <si>
-    <t>25010-0</t>
-  </si>
-  <si>
-    <t>US Thyroid</t>
-  </si>
-  <si>
-    <t>38268-9</t>
-  </si>
-  <si>
-    <t>DXA Skeletal Sys Views for BMD</t>
-  </si>
-  <si>
-    <t>13046-8</t>
-  </si>
-  <si>
-    <t>Atypical lymphocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>13047-6</t>
-  </si>
-  <si>
-    <t>Plasma cells/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>19048-8</t>
-  </si>
-  <si>
-    <t>Erythroblasts/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>26446-5</t>
-  </si>
-  <si>
-    <t>Blasts/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26450-7</t>
-  </si>
-  <si>
-    <t>Eosinophils/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26464-8</t>
-  </si>
-  <si>
-    <t>26478-8</t>
-  </si>
-  <si>
-    <t>Lymphocytes/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26485-3</t>
-  </si>
-  <si>
-    <t>Monocytes/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26498-6</t>
-  </si>
-  <si>
-    <t>Myelocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26505-8</t>
-  </si>
-  <si>
-    <t>Hypersegmented neutrophils/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26508-2</t>
-  </si>
-  <si>
-    <t>Neutrophils/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>26511-6</t>
-  </si>
-  <si>
-    <t>Neutrophils.segmented/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>26515-7</t>
-  </si>
-  <si>
-    <t>Platelets [#/volume] in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>26524-9</t>
-  </si>
-  <si>
-    <t>Promyelocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>28539-5</t>
-  </si>
-  <si>
-    <t>MCH [Entitic mass] by Automated count</t>
-  </si>
-  <si>
-    <t>28541-1</t>
-  </si>
-  <si>
-    <t>Metamyelocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>30180-4</t>
-  </si>
-  <si>
-    <t>Basophils/100 leukocytes in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>30413-9</t>
-  </si>
-  <si>
-    <t>Abnormal lymphocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>30428-7</t>
-  </si>
-  <si>
-    <t>MCV [Entitic volume] by calculation</t>
-  </si>
-  <si>
-    <t>30441-0</t>
-  </si>
-  <si>
-    <t>Abnormal monocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>30466-7</t>
-  </si>
-  <si>
-    <t>Promonocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>34921-7</t>
-  </si>
-  <si>
-    <t>Plasmacytoid lymphocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>5905-5</t>
-  </si>
-  <si>
-    <t>Monocytes/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>70028-6</t>
-  </si>
-  <si>
-    <t>Megakaryocytes/100 leukocytes in Blood</t>
-  </si>
-  <si>
-    <t>706-2</t>
-  </si>
-  <si>
-    <t>Basophils/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>713-8</t>
-  </si>
-  <si>
-    <t>Eosinophils/100 leukocytes in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>731-0</t>
-  </si>
-  <si>
-    <t>Lymphocytes [#/volume] in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>751-8</t>
-  </si>
-  <si>
-    <t>Neutrophils [#/volume] in Blood by Automated count</t>
-  </si>
-  <si>
-    <t>785-6</t>
-  </si>
-  <si>
-    <t>786-4</t>
-  </si>
-  <si>
-    <t>MCHC [Mass/volume] by Automated count</t>
-  </si>
-  <si>
-    <t>787-2</t>
-  </si>
-  <si>
-    <t>MCV [Entitic volume] by Automated count</t>
-  </si>
-  <si>
-    <t>788-0</t>
-  </si>
-  <si>
-    <t>Erythrocyte distribution width [Ratio] by Automated count</t>
-  </si>
-  <si>
-    <t>804-5</t>
-  </si>
-  <si>
-    <t>WBC [#/volume] in Blood by Manual count</t>
-  </si>
-  <si>
-    <t>17861-6</t>
-  </si>
-  <si>
-    <t>Calcium [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>20448-7</t>
-  </si>
-  <si>
-    <t>Insulin [Units/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2428-1</t>
-  </si>
-  <si>
-    <t>Homocysteine [Moles/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>30522-7</t>
-  </si>
-  <si>
-    <t>C reactive protein [Mass/volume] in Serum or Plasma by High sensitivity method</t>
-  </si>
-  <si>
-    <t>3084-1</t>
-  </si>
-  <si>
-    <t>Uric acid [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>33863-2</t>
-  </si>
-  <si>
-    <t>Cystatin C [Mass/volume] in Serum, Plasma or Blood</t>
-  </si>
-  <si>
-    <t>33914-3</t>
-  </si>
-  <si>
-    <t>Glomerular filtration rate/1.73 sq M.predicted by MDRD equation</t>
-  </si>
-  <si>
-    <t>4548-4</t>
-  </si>
-  <si>
-    <t>Hemoglobin A1c/Hemoglobin.total in Blood</t>
-  </si>
-  <si>
-    <t>47214-2</t>
-  </si>
-  <si>
-    <t>Homeostasis model assessment</t>
-  </si>
-  <si>
-    <t>59261-8</t>
-  </si>
-  <si>
-    <t>Hemoglobin A1c/Hemoglobin.total in Blood by IFCC protocol</t>
-  </si>
-  <si>
-    <t>98979-8</t>
-  </si>
-  <si>
-    <t>Glomerular filtration rate [Volume Rate/Area] in Serum, Plasma or Blood by Creatinine-based formula (CKD-EPI 2021)/1.73 sq M</t>
-  </si>
-  <si>
-    <t>10834-0</t>
-  </si>
-  <si>
-    <t>Globulin [Mass/volume] in Serum or Plasma by calculation</t>
-  </si>
-  <si>
-    <t>14390-9</t>
-  </si>
-  <si>
-    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
-  </si>
-  <si>
-    <t>14409-7</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by UV with P5P</t>
-  </si>
-  <si>
-    <t>1742-6</t>
-  </si>
-  <si>
-    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1744-2</t>
-  </si>
-  <si>
-    <t>Alanine aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
-  </si>
-  <si>
-    <t>1751-7</t>
-  </si>
-  <si>
-    <t>Albumin [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1759-0</t>
-  </si>
-  <si>
-    <t>Albumin/Globulin [Mass Ratio] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1783-0</t>
-  </si>
-  <si>
-    <t>Alkaline phosphatase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1798-8</t>
-  </si>
-  <si>
-    <t>Amylase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1920-8</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1968-7</t>
-  </si>
-  <si>
-    <t>Bilirubin.direct [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>1975-2</t>
-  </si>
-  <si>
-    <t>Bilirubin.total [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2532-0</t>
-  </si>
-  <si>
-    <t>Lactate dehydrogenase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2885-2</t>
-  </si>
-  <si>
-    <t>Protein [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>3040-3</t>
-  </si>
-  <si>
-    <t>Lipase [Enzymatic activity/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>6768-6</t>
-  </si>
-  <si>
-    <t>88112-8</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase [Enzymatic activity/volume] in Serum or Plasma by No addition of P-5'-P</t>
-  </si>
-  <si>
-    <t>46986-6</t>
-  </si>
-  <si>
-    <t>Cholesterol in VLDL [Mass/volume] in Serum or Plasma by calculation</t>
-  </si>
-  <si>
-    <t>9830-1</t>
-  </si>
-  <si>
-    <t>Cholesterol/Cholesterol in HDL [Mass Ratio] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2132-9</t>
-  </si>
-  <si>
-    <t>Cobalamin (Vitamin B12) [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>2284-8</t>
-  </si>
-  <si>
-    <t>Folate [Mass/volume] in Serum or Plasma</t>
-  </si>
-  <si>
-    <t>3016-3</t>
-  </si>
-  <si>
-    <t>Thyrotropin [Units/volume] in Serum or Plasma by 3rd IS</t>
-  </si>
-  <si>
     <t>3026-2</t>
   </si>
   <si>
-    <t>Thyroxine (T4) total [Mass/volume] in Serum or Plasma</t>
+    <t>Thyroxine (T4) [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>3051-0</t>
@@ -1245,37 +1272,37 @@
     <t>3053-6</t>
   </si>
   <si>
-    <t>Triiodothyronine (T3) total [Mass/volume] in Serum or Plasma</t>
+    <t>Triiodothyronine (T3) [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>62292-8</t>
   </si>
   <si>
-    <t>25-hydroxyvitamin D3 [Mass/volume] in Serum or Plasma</t>
+    <t>25-Hydroxyvitamin D3+25-Hydroxyvitamin D2 [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>8099-4</t>
   </si>
   <si>
-    <t>Thyroid peroxidase Ab [Units/volume] in Serum or Plasma</t>
+    <t>Thyroperoxidase Ab [Units/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>13950-1</t>
   </si>
   <si>
-    <t>Hepatitis A virus IgM Ab [Presence] in Serum or Plasma</t>
+    <t>Hepatitis A virus IgM Ab [Presence] in Serum or Plasma by Immunoassay</t>
   </si>
   <si>
     <t>13952-7</t>
   </si>
   <si>
-    <t>Hepatitis B virus core Ab [Presence] in Serum or Plasma</t>
+    <t>Hepatitis B virus core Ab [Presence] in Serum or Plasma by Immunoassay</t>
   </si>
   <si>
     <t>17780-8</t>
   </si>
   <si>
-    <t>Helicobacter pylori Ag [Presence] in Stool</t>
+    <t>Helicobacter pylori Ag [Presence] in Stool by Immunoassay</t>
   </si>
   <si>
     <t>20507-0</t>
@@ -1293,7 +1320,7 @@
     <t>22322-2</t>
   </si>
   <si>
-    <t>Hepatitis B virus surface Ab [Units/volume] in Serum</t>
+    <t>Hepatitis B virus surface Ab [Presence] in Serum</t>
   </si>
   <si>
     <t>24110-9</t>
@@ -1311,49 +1338,49 @@
     <t>31147-2</t>
   </si>
   <si>
-    <t>Reagin Ab [Presence] in Serum by RPR -- titer</t>
+    <t>Reagin Ab [Titer] in Serum by RPR</t>
   </si>
   <si>
     <t>5176-3</t>
   </si>
   <si>
-    <t>Helicobacter pylori IgG Ab [Presence] in Serum</t>
+    <t>Helicobacter pylori IgG Ab [Units/volume] in Serum by Immunoassay</t>
   </si>
   <si>
     <t>51913-2</t>
   </si>
   <si>
-    <t>Hepatitis A virus Ab [Presence] in Serum or Plasma</t>
+    <t>Hepatitis A virus IgG+IgM Ab [Presence] in Serum</t>
   </si>
   <si>
     <t>5193-8</t>
   </si>
   <si>
-    <t>Hepatitis B virus surface Ab [Presence] in Serum or Plasma</t>
+    <t>Hepatitis B virus surface Ab [Units/volume] in Serum or Plasma by Immunoassay</t>
   </si>
   <si>
     <t>5334-8</t>
   </si>
   <si>
-    <t>Rubella virus IgG Ab [Units/volume] in Serum or Plasma</t>
+    <t>Rubella virus IgG Ab [Units/volume] in Serum or Plasma by Immunoassay</t>
   </si>
   <si>
     <t>5403-1</t>
   </si>
   <si>
-    <t>Varicella zoster virus IgG Ab [Units/volume] in Serum or Plasma</t>
+    <t>Varicella zoster virus IgG Ab [Units/volume] in Serum by Immunoassay</t>
   </si>
   <si>
     <t>56888-1</t>
   </si>
   <si>
-    <t>HIV 1 and 2 Ag and Ab panel [Presence] in Serum or Plasma</t>
+    <t>HIV 1+2 Ab+HIV1 p24 Ag [Presence] in Serum or Plasma by Immunoassay</t>
   </si>
   <si>
     <t>7962-4</t>
   </si>
   <si>
-    <t>Measles virus IgG Ab [Units/volume] in Serum or Plasma</t>
+    <t>Measles virus IgG Ab [Units/volume] in Serum</t>
   </si>
   <si>
     <t>11218-5</t>
@@ -1371,19 +1398,19 @@
     <t>12453-7</t>
   </si>
   <si>
-    <t>Amorphous phosphate crystals [Presence] in Urine sediment</t>
+    <t>Phosphate crystals amorphous [Presence] in Urine sediment by Light microscopy</t>
   </si>
   <si>
     <t>12454-5</t>
   </si>
   <si>
-    <t>Amorphous urate crystals [Presence] in Urine sediment</t>
+    <t>Urate crystals amorphous [Presence] in Urine sediment by Light microscopy</t>
   </si>
   <si>
     <t>13658-0</t>
   </si>
   <si>
-    <t>Urobilinogen [Presence] in Urine by Test strip</t>
+    <t>Urobilinogen [Presence] in Urine</t>
   </si>
   <si>
     <t>13945-1</t>
@@ -1395,16 +1422,16 @@
     <t>20456-0</t>
   </si>
   <si>
-    <t>Fungi yeast-like [Presence] in Urine sediment</t>
+    <t>Fungi.yeastlike [Presence] in Urine sediment by Light microscopy</t>
   </si>
   <si>
     <t>20621-9</t>
   </si>
   <si>
-    <t>Albumin/Creatinine [Ratio] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>20627-6</t>
+    <t>Albumin/Creatinine [Mass Ratio] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5778-6</t>
   </si>
   <si>
     <t>Color of Urine</t>
@@ -1425,211 +1452,229 @@
     <t>32356-8</t>
   </si>
   <si>
-    <t>Yeast [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>33218-9</t>
-  </si>
-  <si>
-    <t>Bacteria [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33219-7</t>
-  </si>
-  <si>
-    <t>Epithelial cells.squamous [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33223-9</t>
-  </si>
-  <si>
-    <t>Hyaline casts [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>33342-7</t>
-  </si>
-  <si>
-    <t>Epithelial cells [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>43755-8</t>
-  </si>
-  <si>
-    <t>Casts [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>46419-8</t>
-  </si>
-  <si>
-    <t>Erythrocytes [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>46702-7</t>
-  </si>
-  <si>
-    <t>Leukocytes [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>50235-1</t>
-  </si>
-  <si>
-    <t>Mucus [#/volume] in Urine sediment by Automated count</t>
+    <t>Yeast [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>51480-2</t>
+  </si>
+  <si>
+    <t>Bacteria [#/volume] in Urine by Automated count</t>
+  </si>
+  <si>
+    <t>51486-9</t>
+  </si>
+  <si>
+    <t>Epithelial cells.squamous [#/volume] in Urine by Automated count</t>
+  </si>
+  <si>
+    <t>51484-4</t>
+  </si>
+  <si>
+    <t>Hyaline casts [#/volume] in Urine by Automated count</t>
+  </si>
+  <si>
+    <t>87926-2</t>
+  </si>
+  <si>
+    <t>Epithelial cells [#/volume] in Urine by Automated</t>
+  </si>
+  <si>
+    <t>51483-6</t>
+  </si>
+  <si>
+    <t>Casts [#/volume] in Urine by Automated count</t>
+  </si>
+  <si>
+    <t>798-9</t>
+  </si>
+  <si>
+    <t>Erythrocytes [#/volume] in Urine by Automated count</t>
+  </si>
+  <si>
+    <t>51487-7</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/volume] in Urine by Automated count</t>
+  </si>
+  <si>
+    <t>51478-6</t>
+  </si>
+  <si>
+    <t>Mucus [#/volume] in Urine by Automated count</t>
   </si>
   <si>
     <t>50551-1</t>
   </si>
   <si>
-    <t>Bilirubin [Presence] in Urine by Test strip</t>
+    <t>Bilirubin.total [Presence] in Urine by Automated test strip</t>
   </si>
   <si>
     <t>50555-2</t>
   </si>
   <si>
-    <t>Glucose [Presence] in Urine by Test strip</t>
+    <t>Glucose [Presence] in Urine by Automated test strip</t>
   </si>
   <si>
     <t>50558-6</t>
   </si>
   <si>
+    <t>Nitrite [Presence] in Urine by Automated test strip</t>
+  </si>
+  <si>
+    <t>50560-2</t>
+  </si>
+  <si>
+    <t>pH of Urine by Automated test strip</t>
+  </si>
+  <si>
+    <t>50562-8</t>
+  </si>
+  <si>
+    <t>Specific gravity of Urine by Refractometry automated</t>
+  </si>
+  <si>
+    <t>51479-4</t>
+  </si>
+  <si>
+    <t>Spermatozoa [#/volume] in Urine by Automated count</t>
+  </si>
+  <si>
+    <t>53975-9</t>
+  </si>
+  <si>
+    <t>Drug crystals [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>5766-1</t>
+  </si>
+  <si>
+    <t>Ammonium urate crystals [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>5770-3</t>
+  </si>
+  <si>
+    <t>Bilirubin.total [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5771-1</t>
+  </si>
+  <si>
+    <t>Bilirubin crystals [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>5773-7</t>
+  </si>
+  <si>
+    <t>Calcium carbonate crystals [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>57734-6</t>
+  </si>
+  <si>
+    <t>Ketones [Presence] in Urine by Automated test strip</t>
+  </si>
+  <si>
+    <t>5774-5</t>
+  </si>
+  <si>
+    <t>Calcium oxalate crystals [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>5775-2</t>
+  </si>
+  <si>
+    <t>Calcium phosphate crystals [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>57751-0</t>
+  </si>
+  <si>
+    <t>Hemoglobin [Presence] in Urine by Automated test strip</t>
+  </si>
+  <si>
+    <t>5777-8</t>
+  </si>
+  <si>
+    <t>Cholesterol crystals [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>5784-4</t>
+  </si>
+  <si>
+    <t>Cystine crystals [Presence] in Urine sediment by Light microscopy</t>
+  </si>
+  <si>
+    <t>5787-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>5788-5</t>
+  </si>
+  <si>
+    <t>Oval fat bodies (globules) [#/area] in Urine sediment by Microscopy high power field</t>
+  </si>
+  <si>
+    <t>5792-7</t>
+  </si>
+  <si>
+    <t>Glucose [Mass/volume] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5794-3</t>
+  </si>
+  <si>
+    <t>Hemoglobin [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5796-8</t>
+  </si>
+  <si>
+    <t>Hyaline casts [#/area] in Urine sediment by Microscopy low power field</t>
+  </si>
+  <si>
+    <t>5797-6</t>
+  </si>
+  <si>
+    <t>Ketones [Mass/volume] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5799-2</t>
+  </si>
+  <si>
+    <t>Leukocyte esterase [Presence] in Urine by Test strip</t>
+  </si>
+  <si>
+    <t>5802-4</t>
+  </si>
+  <si>
     <t>Nitrite [Presence] in Urine by Test strip</t>
   </si>
   <si>
-    <t>50560-2</t>
+    <t>5803-2</t>
   </si>
   <si>
     <t>pH of Urine by Test strip</t>
   </si>
   <si>
-    <t>50562-8</t>
-  </si>
-  <si>
-    <t>Specific gravity of Urine by Refractometer</t>
-  </si>
-  <si>
-    <t>53324-0</t>
-  </si>
-  <si>
-    <t>Spermatozoa [#/volume] in Urine sediment by Automated count</t>
-  </si>
-  <si>
-    <t>53975-9</t>
-  </si>
-  <si>
-    <t>Drug crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5766-1</t>
-  </si>
-  <si>
-    <t>Ammonium acid urate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5770-3</t>
-  </si>
-  <si>
-    <t>5771-1</t>
-  </si>
-  <si>
-    <t>Bilirubin crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5773-7</t>
-  </si>
-  <si>
-    <t>Calcium carbonate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>57734-6</t>
-  </si>
-  <si>
-    <t>Ketones [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>5774-5</t>
-  </si>
-  <si>
-    <t>Calcium oxalate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5775-2</t>
-  </si>
-  <si>
-    <t>Calcium phosphate crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>57751-0</t>
-  </si>
-  <si>
-    <t>Hemoglobin [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>5777-8</t>
-  </si>
-  <si>
-    <t>Cholesterol crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5784-4</t>
-  </si>
-  <si>
-    <t>Cystine crystals [Presence] in Urine sediment</t>
-  </si>
-  <si>
-    <t>5787-7</t>
-  </si>
-  <si>
-    <t>Epithelial cells [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>5788-5</t>
-  </si>
-  <si>
-    <t>Oval fat bodies [#/area] in Urine sediment by Microscopy high power field</t>
-  </si>
-  <si>
-    <t>5792-7</t>
-  </si>
-  <si>
-    <t>5794-3</t>
-  </si>
-  <si>
-    <t>5796-8</t>
-  </si>
-  <si>
-    <t>Hyaline casts [#/area] in Urine sediment by Microscopy low power field</t>
-  </si>
-  <si>
-    <t>5797-6</t>
-  </si>
-  <si>
-    <t>5799-2</t>
-  </si>
-  <si>
-    <t>Leukocyte esterase [Presence] in Urine by Test strip</t>
-  </si>
-  <si>
-    <t>5802-4</t>
-  </si>
-  <si>
-    <t>5803-2</t>
-  </si>
-  <si>
     <t>5813-1</t>
   </si>
   <si>
-    <t>Trichomonas vaginalis [Presence] in Urine sediment</t>
+    <t>Trichomonas vaginalis [Presence] in Urine sediment by Light microscopy</t>
   </si>
   <si>
     <t>5814-9</t>
   </si>
   <si>
-    <t>Calcium magnesium ammonium phosphate crystals [Presence] in Urine sediment</t>
+    <t>Triple phosphate crystals [Presence] in Urine sediment by Light microscopy</t>
   </si>
   <si>
     <t>5817-2</t>
   </si>
   <si>
-    <t>Uric acid crystals [Presence] in Urine sediment</t>
+    <t>Urate crystals [Presence] in Urine sediment by Light microscopy</t>
   </si>
   <si>
     <t>5821-4</t>
@@ -1641,10 +1686,16 @@
     <t>60026-2</t>
   </si>
   <si>
+    <t>Leukocyte esterase [Presence] in Urine by Automated test strip</t>
+  </si>
+  <si>
     <t>62487-4</t>
   </si>
   <si>
-    <t>13705-9</t>
+    <t>Urobilinogen [Presence] in Urine by Automated test strip</t>
+  </si>
+  <si>
+    <t>9318-7</t>
   </si>
   <si>
     <t>Albumin/Creatinine [Mass Ratio] in Urine</t>
@@ -1677,37 +1728,37 @@
     <t>10701-1</t>
   </si>
   <si>
-    <t>Ova and parasites [Presence] in Stool by Concentration method</t>
+    <t>Ova and parasites identified in Stool by Concentration</t>
   </si>
   <si>
     <t>10704-5</t>
   </si>
   <si>
-    <t>Ova and parasites [Presence] in Stool by Microscopy</t>
+    <t>Ova and parasites identified in Stool by Light microscopy</t>
   </si>
   <si>
     <t>13655-6</t>
   </si>
   <si>
-    <t>Leukocytes [Presence] in Stool by Microscopy</t>
+    <t>Leukocytes [Presence] in Stool by Light microscopy</t>
   </si>
   <si>
     <t>2335-8</t>
   </si>
   <si>
-    <t>Hemoglobin [Presence] in Stool</t>
+    <t>Hemoglobin [Presence] in Stool from gastrointestinal</t>
   </si>
   <si>
     <t>33668-5</t>
   </si>
   <si>
-    <t>Erythrocytes [Presence] in Stool by Microscopy</t>
+    <t>Erythrocytes [Presence] in Stool</t>
   </si>
   <si>
     <t>42524-9</t>
   </si>
   <si>
-    <t>Mucus [Presence] in Stool by Microscopy</t>
+    <t>Mucus [Presence] in Stool by Light microscopy</t>
   </si>
   <si>
     <t>9397-1</t>
@@ -2003,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B282"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2735,1519 +2786,1535 @@
         <v>208</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>203</v>
+        <v>231</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>75</v>
+        <v>289</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>304</v>
+        <v>335</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>377</v>
+        <v>397</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>488</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>490</v>
+        <v>531</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>515</v>
+        <v>533</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>509</v>
+        <v>537</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>492</v>
+        <v>541</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>494</v>
+        <v>543</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>534</v>
+        <v>545</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>536</v>
+        <v>547</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>538</v>
+        <v>549</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>540</v>
+        <v>551</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>530</v>
+        <v>553</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>456</v>
+        <v>555</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>544</v>
+        <v>557</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>546</v>
+        <v>559</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>548</v>
+        <v>561</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>550</v>
+        <v>563</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>552</v>
+        <v>565</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>554</v>
+        <v>567</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>556</v>
+        <v>569</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>558</v>
+        <v>571</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>560</v>
+        <v>573</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>564</v>
+        <v>577</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>566</v>
+        <v>579</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>568</v>
+        <v>581</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>570</v>
+        <v>583</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>22</v>
+        <v>584</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>22</v>
+        <v>585</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>572</v>
+        <v>587</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="608">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1461,48 +1461,96 @@
     <t>Bacteria [#/volume] in Urine by Automated count</t>
   </si>
   <si>
+    <t>33218-9</t>
+  </si>
+  <si>
+    <t>Bacteria [#/area] in Urine sediment by Automated count</t>
+  </si>
+  <si>
     <t>51486-9</t>
   </si>
   <si>
     <t>Epithelial cells.squamous [#/volume] in Urine by Automated count</t>
   </si>
   <si>
+    <t>33219-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells.squamous [#/area] in Urine sediment by Automated count</t>
+  </si>
+  <si>
     <t>51484-4</t>
   </si>
   <si>
     <t>Hyaline casts [#/volume] in Urine by Automated count</t>
   </si>
   <si>
+    <t>33223-9</t>
+  </si>
+  <si>
+    <t>Hyaline casts [#/area] in Urine sediment by Automated count</t>
+  </si>
+  <si>
     <t>87926-2</t>
   </si>
   <si>
     <t>Epithelial cells [#/volume] in Urine by Automated</t>
   </si>
   <si>
+    <t>33342-7</t>
+  </si>
+  <si>
+    <t>Epithelial cells [#/area] in Urine sediment by Automated count</t>
+  </si>
+  <si>
     <t>51483-6</t>
   </si>
   <si>
     <t>Casts [#/volume] in Urine by Automated count</t>
   </si>
   <si>
+    <t>43755-8</t>
+  </si>
+  <si>
+    <t>Casts [#/area] in Urine sediment by Automated count</t>
+  </si>
+  <si>
     <t>798-9</t>
   </si>
   <si>
     <t>Erythrocytes [#/volume] in Urine by Automated count</t>
   </si>
   <si>
+    <t>46419-8</t>
+  </si>
+  <si>
+    <t>Erythrocytes [#/area] in Urine sediment by Automated count</t>
+  </si>
+  <si>
     <t>51487-7</t>
   </si>
   <si>
     <t>Leukocytes [#/volume] in Urine by Automated count</t>
   </si>
   <si>
+    <t>46702-7</t>
+  </si>
+  <si>
+    <t>Leukocytes [#/area] in Urine sediment by Automated count</t>
+  </si>
+  <si>
     <t>51478-6</t>
   </si>
   <si>
     <t>Mucus [#/volume] in Urine by Automated count</t>
   </si>
   <si>
+    <t>50235-1</t>
+  </si>
+  <si>
+    <t>Mucus [#/area] in Urine sediment by Automated count</t>
+  </si>
+  <si>
     <t>50551-1</t>
   </si>
   <si>
@@ -1537,6 +1585,12 @@
   </si>
   <si>
     <t>Spermatozoa [#/volume] in Urine by Automated count</t>
+  </si>
+  <si>
+    <t>53324-0</t>
+  </si>
+  <si>
+    <t>Spermatozoa [#/area] in Urine sediment by Automated count</t>
   </si>
   <si>
     <t>53975-9</t>
@@ -2054,7 +2108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B282"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4303,18 +4357,90 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>22</v>
+        <v>588</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>22</v>
+        <v>589</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B286" t="s" s="2">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B287" t="s" s="2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B288" t="s" s="2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B290" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>包含特殊健康檢查與體格檢查之實驗室與生理功能檢驗項目，以及自費健康檢查常見之影像學檢查（如 MRI、CT、PET/CT、超音波、骨密度等）與內視鏡檢查（如胃鏡、大腸鏡），對應至 LOINC 代碼。</t>
+    <t>【技術規格】包含特殊健康檢查與體格檢查之實驗室與生理功能檢驗項目，以及自費健康檢查常見之影像學檢查（如 MRI、CT、PET/CT、超音波、骨密度等）與內視鏡檢查（如胃鏡、大腸鏡），對應至 LOINC 代碼。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-ExtendedDataset.xlsx
+++ b/ValueSet-VS-ExtendedDataset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
